--- a/Faculty_Proposal_Abstracts.xlsx
+++ b/Faculty_Proposal_Abstracts.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ucirvine.sharepoint.com/sites/BioSci-Contracts&amp;Grants-Team/Shared Documents/BioSci Research Development/Faculty-Keyword-Inventory-Project/faculty-mapped-mesh-terms/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1225" documentId="11_05AA03B0DAF796570A8E46C5BB44859CB1D97C9A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2FFE2C92-B10D-134A-A5C1-D28D9852EE6D}"/>
+  <xr:revisionPtr revIDLastSave="1227" documentId="11_05AA03B0DAF796570A8E46C5BB44859CB1D97C9A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{58D6868C-A225-4AD2-B4AD-64915ED20BFA}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="28960" yWindow="-2940" windowWidth="40640" windowHeight="20780" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="28960" yWindow="-2940" windowWidth="40640" windowHeight="20780" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Pre-Award README" sheetId="1" r:id="rId1"/>
@@ -2300,6 +2300,9 @@
   </si>
   <si>
     <t xml:space="preserve">It is with great enthusiasm and gratitude that we submit this proposal for funding to the Diane and Guilford Glazer Foundation. As you know, the UC Irvine Institute for Memory Impairments and Neurological Disorders (UCI MIND) is a world-renowned research organization devoted to the study of Alzheimer’s disease (AD) and Alzheimer’s disease-related dementias (ADRD). This includes a more than 30 year history of being at the cutting edge of discoveries related to AD/ADRD. Our more than 50 renowned faculty include basic and well as clinical research scientists and the mission of UCI MIND is to bring these transdisciplinary investigators together to perform collaborative and indeed synergistic research to accelerate pursuit of solutions for these burdensome neurodegenerative diseases.  In this proposal titled “Investigating Mild Behavior Impairment,” we propose to leverage our cohort of more than 300 individuals who have enrolled in longitudinal observational research at UCI MIND to better elucidate the earliest symptoms associated with AD/ADRD.  Mild Behavior Impairment (MBI) is a relatively recently developed clinical construct, proposed to ensure that patients with neurological conditions such as Alzheimer’s who do not first present with typical symptoms such as memory loss are not missed. MBI can include subtle behavioral symptoms such as apathy, anxiety, anhedonia, and depression, as well as more overt symptoms such as agitation, delusions, hallucinations, and changes in personality. In all cases, patients with MBI are at risk for misdiagnosis as late onset psychiatric conditions (e.g., schizophrenia) when in fact they suffer from a neurodegenerative condition such as AD. UCI MIND Director of Clinical Research Dr. David Sultzer is a geriatric psychiatrist and an international leader and collaborative architect of the MBI construct. In the work funded by the Glazer Foundation, Dr. Sultzer will lead innovative research to better understand MBI at UCI.  Dr. Sultzer aided in the developing the “MBI checklist” a novel tool to better capture the presence or absence of mild behavioral symptoms in people with or at risk for cognitive impairment and dementia. With support from the Glazer Foundation, we will collect the MBI checklist from our entire research cohort and perform a variety of novel analyses not otherwise possible. These will include: • Determine whether MBI severity is associated with diagnostic categories. Among our cohort of participants, some are unimpaired, some have mild cognitive impairment (MCI), and some have full blown dementia. We will assess whether the severity of MBI is associated with these diagnostic categories, assessing the hypothesis that greater diagnostic severity is associated with greater MBI severity.  • Assess the relationship between MBI and AD biomarkers in the cerebrospinal fluid. In addition to our large cohort of participants, UCI MIND has a long and successful history of securing biomarker assessments, including measures of cerebrospinal fluid (CSF; examined through lumbar puncture), from research participants. This positions us to assess the relationship between MBI severity and AD biomarkers in CSF (amyloid beta [Ab], phosphorylated tau [p-tau], and total tau[t-tau]). We will begin by determining whether such relationships exist, particularly among individuals who do not meet clinical criteria for MCI or dementia. We hypothesize that MBI severity is associated with a biomarker signature in CSF among individuals who do not meet diagnostic criteria for AD.  • Determine the longitudinal course of MBI. Requiring multiple years of follow-up, we will be well positioned to understand the stability and importance of change over time in MBI presentation. We plan to assess MBI routinely in our large annual follow-up longitudinal study. We anticipate that this will allow UCI MIND to produce some of the first findings based on longitudinal assessments in the field. We hypothesize that changes in MBI will precede cognitive changes, particularly in participants with no demonstrable cognitive impairment.  In conclusion, with support from the Glazer Foundation, UCI MIND will be positioned to continue our leadership in AD/ADRD research, particularly in the area of MBI. We would be thrilled to establish periodic reports, including in-person presentations of our progress to the Foundation leadership and look forward to a productive long-term relationship.  </t>
+  </si>
+  <si>
+    <t>Humans; Aged; Amyloid beta-Peptides; Neurodegenerative Diseases; Apathy; Schizophrenia; Spinal Puncture; Leadership; Anhedonia; Alzheimer Disease; Checklist; Follow-Up Studies; Delusions; Depression; Longitudinal Studies; Psychiatrists; Cognitive Dysfunction; Anxiety; Memory Disorders; Hallucinations; Faculty; Cognition; Biomarkers; Diagnostic Errors</t>
   </si>
   <si>
     <t xml:space="preserve">Overview The proper functioning of cells depends on the precise distribution of proteins within different cellular compartments. However, technical obstacles in subcellular spatial proteomics restrict our ability to fully investigate the subcellular realm. Imaging-based proteomics provides high spatial resolution, but has low multiplexity and is biased by antibodies. On the other hand, mass spectrometry (MS)-based proteomics offers unbiased whole proteome but has low resolution. Subcellular resolution of protein isolation remains a key challenge for spatial proteomics. The overall objective of this project is to develop an unbiased subcellular proteomics method, called Optogel Proteomics. Our core concept consists of linking proteins to hydrogel using photocleavable crosslinkers and using a two-photon microscope to accurately delink proteins in subcellular areas of interest through accurate photocleavage. This allows us to release the proteins from the targeted regions for unbiased MS analysis. We plan to validate Optogel Proteomics with an application in nuclear lamina. Recent super- resolution microscopy results uncovered submicron-sized lamina substructures the overall lamina meshwork. These substructures are phenotypes of cancer cells, which are associated with heterochromatin loss. However, their protein composition is unclear blocking our understanding of their functions. We propose to analyze the proteome of lamina substructures using Optogel Proteomics, and validate results with Label-Retention Expansion Microscopy (LR-ExM), which is a super-resolution microscopy method we developed for deep cell imaging. Intellectual merit This project brings together ground-breaking novel technology and new biology. First, our Optogel Proteomics development will advance bioengineering by addressing the resolution challenge in spatial proteomics. Distinct from any existing methods, this method offers the highest spatial resolution for protein isolation in a “what you see is what you get” manner. Second, through the application of Optogel Proteomics in nuclear lamina, we aim to advance cell biology by providing the unbiased proteome of sub-lamina structures, which is currently unachievable. This will elucidate molecular mechanisms of how nuclear lamina regulates heterochromatin, and provide potential drug targets for cancers. Third, using LR-ExM imaging to confirm the results of Optogel Proteomics, we will provide to the science community a validated biotechnology for discoveries of the molecular nature of subcellular structures. Broader Impacts The PI aims to make broader impacts in two key areas: the society’s research capacity and education. First, the goal is to disseminate low-cost molecular resolution LR-ExM to increase research capacity in life science and bioengineering. I have leveraged external funding to distribute the LR-ExM across the US and nine other countries for free for two years. In addition, I plan to operate annually workshop on LR-ExM at the imaging centers of UCI and Institut Pasteur de Montevideo. Second, as a woman scientist who benefited from interdisciplinary training, I am committed to ameliorating the gender gap at the interface of biology, physics, and chemistry. I propose holding annual Women in Interdisciplinary Science (WISe) camps on “engineering and chemical approaches to life sciences” in collaboration with the Lab for Fluorescence Dynamics at UCI. The goal of the workshops is letting next generation women scientists experience interdisciplinary science and understand the career pathway in interdisciplinary science. I will engage my trainees in demonstrating and coaching in both LR-ExM dissemination and WISe programs. Therefore, these educational activities will not only broaden the impact of my research in the society but also will benefit my trainees with teaching and mentoring experience. </t>
@@ -2556,9 +2559,6 @@
   </si>
   <si>
     <t>Given the high incidence of COVID-19 neurological symptoms and the risk of long-term neuropathology in susceptible populations of patients, it is imperative to characterize the effects of SARS-CoV2 on brain cells, to elucidate the mechanisms underlying these effects, and to identify the populations susceptible to neurologic disease following infection. Equally important is to establish the relationships between SARS-CoV2 invasiveness and neurotropism on one hand, and the intrinsic ability of neural cells to mount an anti-viral response and clear up the virus on the other hand. Down Syndrome (DS) represents one of the most susceptible populations of COVID-19 patients, and thus a unique human genetic condition for investigating the cellular and molecular mechanisms underlying susceptibility of neurologically vulnerable individuals to SARSCoV2 infection. We hypothesize that neuro-invasiveness of SARS-CoV2 is facilitated in persons with DS due to neuroinflammation-driven disruption of the blood-brain barrier (BBB), which in turn increases the probability of direct SARS-CoV2 infection of neural cells. Once in the brain, the ability of SARS-CoV2 to infect and replicate will depend on the basal and induced interferon system activity, which ultimately will define the consequences of infection for Alzheimer’s disease (AD) neuropathology. The interferon system hyperactivation in DS might have a complex multiphasic effect on the outcome of SARS-CoV2 infection. To test this hypothesis, we propose three Specific Aims: (2) (1) To elucidate the mechanistic relationships between the susceptibility of human cortical cells to SARS-CoV-2 infection and interferon system activity in these cells; To investigate the acute and longer-lasting consequences of viral infection on AD pathological hallmarks in trisomy-21 (T21) cortical cultures and brain specimens; (3) In a cohort of DS patients, to investigate the relationships between plasma biomarkers that reflect interferon system activity and A myloidT auN eurodegeneration AT(N) biomarkers that reflect AD pathology. We will employ a multidisciplinary and complementary approach, which includes in vitro studies, studies of postmortem brain specimens, and analyses of dataset and clinical plasma biomarkers. Combination of biochemical and molecular biology methods, super resolution confocal microscopy and existing clinical dataset analyses will be used to elucidate the relationships between inter-dependent mechanisms that underly neuroinvasiveness of SARS-CoV2, AD neuropathology in DS and the interferon system-mediated anti-viral defense mechanisms. Understanding these relationships is critical to predict infection outcome and to develop therapeutic strategies for protecting the vulnerable nervous system from virus-mediated damage.</t>
-  </si>
-  <si>
-    <t>Humans; Aged; Amyloid beta-Peptides; Neurodegenerative Diseases; Apathy; Schizophrenia; Spinal Puncture; Leadership; Anhedonia; Alzheimer Disease; Checklist; Follow-Up Studies; Delusions; Depression; Longitudinal Studies; Psychiatrists; Cognitive Dysfunction; Anxiety; Memory Disorders; Hallucinations; Faculty; Cognition; Biomarkers; Diagnostic Errors</t>
   </si>
   <si>
     <t xml:space="preserve">We seek to define how early oncogenic outgrowths are recognized and pruned by the immune system during basal cell carcinoma (BCC) progression and regression, providing new insight into potential immunotherapies for this skin cancer that affects over 4 million patients each year in the U.S. Phenotypically normal human skin often contains oncogenic clones that have known drivers of tumorigenesis, suggesting a surveillance mechanism that prevents oncogenic outgrowths from transitioning into large, palpable tumors. This rare transition in BCC typically requires a high mutational load to break through barriers of tumor growth, where driver mutations are sufficient to drive microtumor growth but not macrotumor growth. How skin actively prevents macrotumor growth and drives regression of existing microtumors are unknown. 
@@ -4136,9 +4136,6 @@
     <t>Humans; Adult; Female; Mice; Animals; Infant; Microglia; Tissue Distribution; Intermediate Filaments; Gliosis; Myelin Basic Protein; Research Design; Grassland; Brain; Neurons; Intracranial Hemorrhages; Calcinosis; RNA</t>
   </si>
   <si>
-    <t>Carmen</t>
-  </si>
-  <si>
     <t xml:space="preserve">Nitrogenase is a complex metalloenzyme central to the global nitrogen cycle, catalyzing the reduction of atmospheric nitrogen to bioavailable ammonia. Termed biological nitrogen fixation, this fundamental process provides ~200 million tons of reduced nitrogen annually, sustaining Earth's ecosystems. Despite decades of research, the (1) enzymatic mechanism and (2) heterologous expression of nitrogenase remain elusive, presenting opportunities for innovation. With respect to 1, the traditional mechanistic thinking of nitrogenase has been driven by the presumption of a structurally ‘static’ cofactor during catalysis. Our recent structural observation of asymmetric belt-sulfur displacements with distinct dinitrogen species in the two cofactors of Mo-nitrogenase invokes a novel mechanism of N2 reduction that necessitates dynamic structural rearrangements of the cofactors during catalysis. In the next 5 years, we will use genetic, biochemical, spectroscopic and structural approaches to probe this novel reaction mechanism, demonstrating the stepwise N2 reduction at the three belt-sulfur sites of each cofactor and illustrating the alternate interaction between the two components of Mo-nitrogenase that drives the coordinated reaction sequences via asynchronous rotation of the two cofactors. These studies will establish a much-needed framework for further exploration of the intricate reaction mechanism of nitrogenase and, in the long run, facilitate the development of nitrogenase-based applications. With respect to 2, efforts to heterologous express nitrogenase have been focused on introducing a complete gene set into a foreign host like E. coli via a ‘top-down’ approach. However, this approach faces challenges in ensuring proper assembly of the key intermediates that eventually give rise to a functional nitrogenase. Our recently developed ‘bottom-up’ strategy allowed a systematic reconstruction of the nitrogenase assembly pathway in E. coli and the ultimate expression of an active prototype nitrogenase, albeit with reduced activity under anaerobic conditions. In the next 5 years, we will use protein-engineering and synthetic-biology methods to enhance the functionality of our prototype nitrogen-fixing system through optimization of the nitrogenase assembly pathway, engineering of the electron and energy supplies in the E. coli host, and implementation of the mechanism of oxygen tolerance in this expression system. These efforts will provide strategies that can also be applied to the heterologous expression of other complex metalloenzymes, thereby advancing both fundamental science and general biotechnological innovation. </t>
   </si>
   <si>
@@ -4152,6 +4149,42 @@
   </si>
   <si>
     <t>HcHenry, Matthew</t>
+  </si>
+  <si>
+    <t>Overview: Forage fishes are critical to global fisheries and ecosystems, relying on schooling behav-
+ior for survival. Schooling enhances mate and prey detection, predator avoidance, and reduces
+energetic costs through coordinated locomotion. This behavior, driven by sensory integration,
+skeletal flexibility, and metabolic regulation, is increasingly vulnerable to ocean acidification, which
+has been shown to impair individual traits like skeletal structure and metabolic rates. However, the
+broader impact of these physiological disruptions on collective schooling behavior remains poorly
+understood. This project aims to address this gap by investigating the effects of ocean acidification
+on the schooling dynamics and swimming performance of the Inland silverside Menidia beryllina,
+focusing on both short-term (within a lifespan) and long-term (across generations) impacts on
+morphology, energetics, and kinematics. The research will provide valuable insights into how
+climate change stressors affect critical collective behaviors that underpin the survival of forage fish
+species.
+Intellectual Merit: This study will advance our understanding of how ocean acidification affects
+not just individual traits, but the collective behavior of forage fish. By integrating biomechanical,
+physiological, and ecological approaches, the research will explore how acidification-induced
+changes in skeletal structure and sensory function influence schooling behavior. The project will
+quantify alterations in collective dynamics and metabolic costs associated with changes in school
+geometry, shedding light on the potential for acclimation both within and across generations. These
+findings will contribute to broader ecological models and inform predictions on how marine ecosys-
+tems respond to climate change, moving beyond individual-level analyses to group dynamics in
+ecologically critical species.
+Broader Impacts: The maintenance of schooling behavior is fundamental for the survival of forage
+fishes, which in turn support entire marine food webs. By investigating how ocean acidification
+disrupts this behavior, this project will inform conservation strategies and fisheries management.
+Understanding the potential for acclimation and resilience in key forage species will help forecast
+ecosystem-level responses to environmental stressors. Furthermore, the project will offer train-
+ing opportunities for students in climate change biology, behavioral ecology, and biomechanics,
+contributing to the development of future integrative biologists. Outreach efforts, including the
+integration of immersive virtual reality simulations of fish schooling behavior, will promote public
+understanding of the effects of climate change on marine life, enhancing engagement in marine
+conservation.</t>
+  </si>
+  <si>
+    <t>Animals; Ecosystem; Food Chain; Climate Change; Mass Behavior; Swimming; Biomechanical Phenomena; Hydrogen-Ion Concentration; Fisheries; Longevity; Resilience, Psychological; Ocean Acidification; Seawater; Fishes; Sensation; Students; Virtual Reality; Acclimatization; Group Dynamics; Biology; Schools</t>
   </si>
   <si>
     <t>Drug abuse and addiction represent major health issues both in the United States and worldwide. In 
@@ -4185,6 +4218,9 @@
   </si>
   <si>
     <t>Humans; United States; Cannabis; Cannabinoids; Public Health; Research Design; Longevity; N-nitrosoiminodiacetic acid; Follow-Up Studies; Goals; Reproducibility of Results; Speech; Schools; Substance-Related Disorders; Psychiatry; Students; Faculty; Delivery of Health Care</t>
+  </si>
+  <si>
+    <t>Carmen</t>
   </si>
   <si>
     <t>It is well-established that STEM fields have traditionally been exclusionary spaces, with the 
@@ -4962,8 +4998,7 @@
     <t>Rebekah</t>
   </si>
   <si>
-    <t>LAY SUMMARY
-While the brain is considered immune privileged, a growing body of evidence has shown that peripheral macrophages can influence the development of many neurological disorders including Parkinson's disease, Multiple Sclerosis, Frontotemporal Dementia, and Alzheimer's Disease (AD). Yet the mechanisms and cell types that mediate these effects remain unclear. In the current project, we will take advantage of chimeric mouse modeling to examine the effects of beta-amyloid depositions on human microglia and monocytes within the brain. This approach will allow us to determine the effects of amyloid plaques on both brain-resident and brain-infiltrating immune cells while also studying the functional genetics and biology of human cells. Using 'spatial genomic' approaches we also examine the interactions between engrafted human immune cells and other key cell types in the brain to determine the impact of peripheral inflammation on AD pathology and neuronal function.</t>
+    <t>While the brain is considered immune privileged, a growing body of evidence has shown that peripheral macrophages can influence the development of many neurological disorders including Parkinson's disease, Multiple Sclerosis, Frontotemporal Dementia, and Alzheimer's Disease (AD). Yet the mechanisms and cell types that mediate these effects remain unclear. In the current project, we will take advantage of chimeric mouse modeling to examine the effects of beta-amyloid depositions on human microglia and monocytes within the brain. This approach will allow us to determine the effects of amyloid plaques on both brain-resident and brain-infiltrating immune cells while also studying the functional genetics and biology of human cells. Using 'spatial genomic' approaches we also examine the interactions between engrafted human immune cells and other key cell types in the brain to determine the impact of peripheral inflammation on AD pathology and neuronal function.</t>
   </si>
   <si>
     <t>Humans; Mice; Animals; Monocytes; Microglia; Alzheimer Disease; Frontotemporal Dementia; Multiple Sclerosis; Plaque, Amyloid; Parkinson Disease; Macrophages; Brain; Inflammation; Genomics</t>
@@ -4975,8 +5010,7 @@
     <t>Humans; Wildfires; Needs Assessment; Climate Change; Droughts; Feasibility Studies; Hot Temperature; Interdisciplinary Research; Private Sector; Resilience, Psychological; Universities; Government; Government Agencies; Risk Assessment; Workforce; Policy; Social Planning</t>
   </si>
   <si>
-    <t>PROJECT NARRATIVE
-Disruption of learning and memory is one of the most common features of neuropsychiatric disorders, and one of the most frequent repercussions of aging. While cortical memory consolidation is a key aspect of learning, the precise mechanisms underlying this process are poorly understood. We propose to use innovative technologies to determine the role of the posterior parietal cortex, a cognitive hub in the mammalian brain, in learning and memory consolidation.</t>
+    <t>Disruption of learning and memory is one of the most common features of neuropsychiatric disorders, and one of the most frequent repercussions of aging. While cortical memory consolidation is a key aspect of learning, the precise mechanisms underlying this process are poorly understood. We propose to use innovative technologies to determine the role of the posterior parietal cortex, a cognitive hub in the mammalian brain, in learning and memory consolidation.</t>
   </si>
   <si>
     <t>Animals; Memory Consolidation; Brain; Parietal Lobe; Aging; Cognition</t>
@@ -4985,6 +5019,9 @@
     <t>Lutterschmidt, Deborah</t>
   </si>
   <si>
+    <t>Eom, Dae Seok</t>
+  </si>
+  <si>
     <t>Jason</t>
   </si>
   <si>
@@ -4997,6 +5034,9 @@
     <t>Demuro, Angelo</t>
   </si>
   <si>
+    <t xml:space="preserve">Garcia Vedrenne, Ana </t>
+  </si>
+  <si>
     <t>? June</t>
   </si>
   <si>
@@ -5031,55 +5071,13 @@
   </si>
   <si>
     <t>Pratt, Jessica</t>
-  </si>
-  <si>
-    <t>Overview: Forage fishes are critical to global fisheries and ecosystems, relying on schooling behav-
-ior for survival. Schooling enhances mate and prey detection, predator avoidance, and reduces
-energetic costs through coordinated locomotion. This behavior, driven by sensory integration,
-skeletal flexibility, and metabolic regulation, is increasingly vulnerable to ocean acidification, which
-has been shown to impair individual traits like skeletal structure and metabolic rates. However, the
-broader impact of these physiological disruptions on collective schooling behavior remains poorly
-understood. This project aims to address this gap by investigating the effects of ocean acidification
-on the schooling dynamics and swimming performance of the Inland silverside Menidia beryllina,
-focusing on both short-term (within a lifespan) and long-term (across generations) impacts on
-morphology, energetics, and kinematics. The research will provide valuable insights into how
-climate change stressors affect critical collective behaviors that underpin the survival of forage fish
-species.
-Intellectual Merit: This study will advance our understanding of how ocean acidification affects
-not just individual traits, but the collective behavior of forage fish. By integrating biomechanical,
-physiological, and ecological approaches, the research will explore how acidification-induced
-changes in skeletal structure and sensory function influence schooling behavior. The project will
-quantify alterations in collective dynamics and metabolic costs associated with changes in school
-geometry, shedding light on the potential for acclimation both within and across generations. These
-findings will contribute to broader ecological models and inform predictions on how marine ecosys-
-tems respond to climate change, moving beyond individual-level analyses to group dynamics in
-ecologically critical species.
-Broader Impacts: The maintenance of schooling behavior is fundamental for the survival of forage
-fishes, which in turn support entire marine food webs. By investigating how ocean acidification
-disrupts this behavior, this project will inform conservation strategies and fisheries management.
-Understanding the potential for acclimation and resilience in key forage species will help forecast
-ecosystem-level responses to environmental stressors. Furthermore, the project will offer train-
-ing opportunities for students in climate change biology, behavioral ecology, and biomechanics,
-contributing to the development of future integrative biologists. Outreach efforts, including the
-integration of immersive virtual reality simulations of fish schooling behavior, will promote public
-understanding of the effects of climate change on marine life, enhancing engagement in marine
-conservation.</t>
-  </si>
-  <si>
-    <t>Animals; Ecosystem; Food Chain; Climate Change; Mass Behavior; Swimming; Biomechanical Phenomena; Hydrogen-Ion Concentration; Fisheries; Longevity; Resilience, Psychological; Ocean Acidification; Seawater; Fishes; Sensation; Students; Virtual Reality; Acclimatization; Group Dynamics; Biology; Schools</t>
-  </si>
-  <si>
-    <t>Eom, Dae Seok</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Garcia Vedrenne, Ana </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="14">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -5578,93 +5576,93 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="B2:C22"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:2" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:2" ht="18" customHeight="1">
       <c r="B2" s="4" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="2:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:2" ht="18" customHeight="1">
       <c r="B3" s="5" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="2:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:2" ht="18" customHeight="1">
       <c r="B4" s="6" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="2:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:2" ht="18" customHeight="1">
       <c r="B5" s="7" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="2:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:2" ht="18" customHeight="1">
       <c r="B6" s="8" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="2:2" ht="18" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="8" spans="2:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:2" ht="18" customHeight="1"/>
+    <row r="8" spans="2:2" ht="18" customHeight="1">
       <c r="B8" s="6" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="2:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:2" ht="18" customHeight="1">
       <c r="B9" s="7" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="2:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:2" ht="18" customHeight="1">
       <c r="B10" s="8" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="2:2" ht="18" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="12" spans="2:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:2" ht="18" customHeight="1"/>
+    <row r="12" spans="2:2" ht="18" customHeight="1">
       <c r="B12" s="5" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="2:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:2" ht="18" customHeight="1">
       <c r="B13" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="2:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:2" ht="18" customHeight="1">
       <c r="B14" s="7" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="2:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:2" ht="18" customHeight="1">
       <c r="B15" s="7" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="2:2" ht="18" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="17" spans="2:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:2" ht="18" customHeight="1"/>
+    <row r="17" spans="2:3" ht="18" customHeight="1">
       <c r="B17" s="6" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="18" spans="2:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:3" ht="18" customHeight="1">
       <c r="B18" s="6" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="19" spans="2:3" ht="18" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="20" spans="2:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:3" ht="18" customHeight="1"/>
+    <row r="20" spans="2:3" ht="18" customHeight="1">
       <c r="B20" s="6" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="21" spans="2:3" ht="18" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="22" spans="2:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:3" ht="18" customHeight="1"/>
+    <row r="22" spans="2:3" ht="18" customHeight="1">
       <c r="C22" s="9"/>
     </row>
   </sheetData>
@@ -5678,13 +5676,13 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:B6"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="24.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="46.83203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="46.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" ht="18" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>15</v>
       </c>
@@ -5692,7 +5690,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:2" ht="18" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>17</v>
       </c>
@@ -5700,7 +5698,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:2" ht="18" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>19</v>
       </c>
@@ -5708,7 +5706,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:2" ht="18" customHeight="1">
       <c r="A4" s="1" t="s">
         <v>21</v>
       </c>
@@ -5716,7 +5714,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:2" ht="18" customHeight="1">
       <c r="A5" s="1" t="s">
         <v>23</v>
       </c>
@@ -5724,7 +5722,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
         <v>25</v>
       </c>
@@ -5749,17 +5747,17 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:G598"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="27" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.6640625" style="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.7109375" style="11" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.83203125" style="12" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="99.6640625" customWidth="1"/>
-    <col min="7" max="7" width="255.83203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.85546875" style="12" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="99.7109375" customWidth="1"/>
+    <col min="7" max="7" width="255.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" ht="18" customHeight="1">
       <c r="A1" t="s">
         <v>27</v>
       </c>
@@ -5782,7 +5780,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7" ht="18" customHeight="1">
       <c r="B2" t="s">
         <v>34</v>
       </c>
@@ -5800,7 +5798,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7" ht="18" customHeight="1">
       <c r="B3" t="s">
         <v>38</v>
       </c>
@@ -5818,7 +5816,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7" ht="18" customHeight="1">
       <c r="B4" t="s">
         <v>42</v>
       </c>
@@ -5835,7 +5833,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7" ht="18" customHeight="1">
       <c r="B5" t="s">
         <v>46</v>
       </c>
@@ -5852,7 +5850,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7" ht="18" customHeight="1">
       <c r="B6" t="s">
         <v>49</v>
       </c>
@@ -5869,7 +5867,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7" ht="18" customHeight="1">
       <c r="B7" t="s">
         <v>52</v>
       </c>
@@ -5887,7 +5885,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7" ht="18" customHeight="1">
       <c r="B8" t="s">
         <v>55</v>
       </c>
@@ -5905,7 +5903,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7" ht="18" customHeight="1">
       <c r="B9" t="s">
         <v>58</v>
       </c>
@@ -5925,7 +5923,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7" ht="18" customHeight="1">
       <c r="B10" t="s">
         <v>61</v>
       </c>
@@ -5943,7 +5941,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7" ht="18" customHeight="1">
       <c r="B11" t="s">
         <v>64</v>
       </c>
@@ -5961,7 +5959,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7" ht="18" customHeight="1">
       <c r="B12" t="s">
         <v>67</v>
       </c>
@@ -5979,7 +5977,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7" ht="18" customHeight="1">
       <c r="B13" t="s">
         <v>70</v>
       </c>
@@ -5997,7 +5995,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7" ht="18" customHeight="1">
       <c r="B14" t="s">
         <v>73</v>
       </c>
@@ -6015,7 +6013,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7" ht="18" customHeight="1">
       <c r="B15" t="s">
         <v>34</v>
       </c>
@@ -6033,7 +6031,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7" ht="18" customHeight="1">
       <c r="B16" t="s">
         <v>78</v>
       </c>
@@ -6051,7 +6049,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="17" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:7" ht="18" customHeight="1">
       <c r="B17" t="s">
         <v>81</v>
       </c>
@@ -6069,7 +6067,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="18" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:7" ht="18" customHeight="1">
       <c r="B18" t="s">
         <v>84</v>
       </c>
@@ -6087,7 +6085,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="19" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:7" ht="18" customHeight="1">
       <c r="B19" t="s">
         <v>87</v>
       </c>
@@ -6105,7 +6103,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="20" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:7" ht="18" customHeight="1">
       <c r="B20" t="s">
         <v>90</v>
       </c>
@@ -6123,7 +6121,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="21" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:7" ht="18" customHeight="1">
       <c r="B21" t="s">
         <v>93</v>
       </c>
@@ -6141,7 +6139,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="22" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:7" ht="18" customHeight="1">
       <c r="B22" t="s">
         <v>96</v>
       </c>
@@ -6159,7 +6157,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="23" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:7" ht="18" customHeight="1">
       <c r="B23" t="s">
         <v>78</v>
       </c>
@@ -6177,7 +6175,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="24" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:7" ht="18" customHeight="1">
       <c r="B24" t="s">
         <v>84</v>
       </c>
@@ -6195,7 +6193,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="25" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:7" ht="18" customHeight="1">
       <c r="B25" t="s">
         <v>73</v>
       </c>
@@ -6213,7 +6211,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="26" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:7" ht="18" customHeight="1">
       <c r="B26" t="s">
         <v>105</v>
       </c>
@@ -6231,7 +6229,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="27" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:7" ht="18" customHeight="1">
       <c r="B27" t="s">
         <v>108</v>
       </c>
@@ -6251,7 +6249,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="28" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:7" ht="18" customHeight="1">
       <c r="B28" t="s">
         <v>112</v>
       </c>
@@ -6271,7 +6269,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="29" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="2:7" ht="18" customHeight="1">
       <c r="B29" t="s">
         <v>46</v>
       </c>
@@ -6289,7 +6287,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="30" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="2:7" ht="18" customHeight="1">
       <c r="B30" t="s">
         <v>117</v>
       </c>
@@ -6307,7 +6305,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="31" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="2:7" ht="18" customHeight="1">
       <c r="B31" t="s">
         <v>120</v>
       </c>
@@ -6325,7 +6323,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="32" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="2:7" ht="18" customHeight="1">
       <c r="B32" t="s">
         <v>120</v>
       </c>
@@ -6343,7 +6341,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="33" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:7" ht="18" customHeight="1">
       <c r="B33" t="s">
         <v>96</v>
       </c>
@@ -6361,7 +6359,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="34" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:7" ht="18" customHeight="1">
       <c r="B34" t="s">
         <v>120</v>
       </c>
@@ -6379,7 +6377,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="35" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:7" ht="18" customHeight="1">
       <c r="B35" t="s">
         <v>129</v>
       </c>
@@ -6397,7 +6395,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="36" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="2:7" ht="18" customHeight="1">
       <c r="B36" t="s">
         <v>132</v>
       </c>
@@ -6415,7 +6413,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="37" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:7" ht="18" customHeight="1">
       <c r="B37" t="s">
         <v>135</v>
       </c>
@@ -6435,7 +6433,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="38" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:7" ht="18" customHeight="1">
       <c r="B38" t="s">
         <v>73</v>
       </c>
@@ -6453,7 +6451,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="39" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:7" ht="18" customHeight="1">
       <c r="B39" t="s">
         <v>52</v>
       </c>
@@ -6471,7 +6469,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="40" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:7" ht="18" customHeight="1">
       <c r="B40" t="s">
         <v>52</v>
       </c>
@@ -6489,7 +6487,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="41" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:7" ht="18" customHeight="1">
       <c r="B41" t="s">
         <v>144</v>
       </c>
@@ -6507,7 +6505,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="42" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:7" ht="18" customHeight="1">
       <c r="B42" t="s">
         <v>87</v>
       </c>
@@ -6525,7 +6523,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="43" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:7" ht="18" customHeight="1">
       <c r="B43" t="s">
         <v>87</v>
       </c>
@@ -6543,7 +6541,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="44" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:7" ht="18" customHeight="1">
       <c r="B44" t="s">
         <v>151</v>
       </c>
@@ -6561,7 +6559,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="45" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:7" ht="18" customHeight="1">
       <c r="B45" t="s">
         <v>105</v>
       </c>
@@ -6579,7 +6577,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="46" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:7" ht="18" customHeight="1">
       <c r="B46" t="s">
         <v>156</v>
       </c>
@@ -6597,7 +6595,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="47" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:7" ht="18" customHeight="1">
       <c r="B47" t="s">
         <v>64</v>
       </c>
@@ -6615,7 +6613,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="48" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:7" ht="18" customHeight="1">
       <c r="B48" t="s">
         <v>64</v>
       </c>
@@ -6633,7 +6631,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="49" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="2:7" ht="18" customHeight="1">
       <c r="B49" t="s">
         <v>163</v>
       </c>
@@ -6651,7 +6649,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="50" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="2:7" ht="18" customHeight="1">
       <c r="B50" t="s">
         <v>166</v>
       </c>
@@ -6671,7 +6669,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="51" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="2:7" ht="18" customHeight="1">
       <c r="B51" t="s">
         <v>78</v>
       </c>
@@ -6689,7 +6687,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="52" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="2:7" ht="18" customHeight="1">
       <c r="B52" t="s">
         <v>171</v>
       </c>
@@ -6707,7 +6705,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="53" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="2:7" ht="18" customHeight="1">
       <c r="B53" t="s">
         <v>156</v>
       </c>
@@ -6725,7 +6723,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="54" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="2:7" ht="18" customHeight="1">
       <c r="B54" t="s">
         <v>176</v>
       </c>
@@ -6743,7 +6741,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="55" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="2:7" ht="18" customHeight="1">
       <c r="B55" t="s">
         <v>179</v>
       </c>
@@ -6761,7 +6759,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="56" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="2:7" ht="18" customHeight="1">
       <c r="B56" t="s">
         <v>42</v>
       </c>
@@ -6779,7 +6777,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="57" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="2:7" ht="18" customHeight="1">
       <c r="B57" t="s">
         <v>163</v>
       </c>
@@ -6797,7 +6795,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="58" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="2:7" ht="18" customHeight="1">
       <c r="B58" t="s">
         <v>163</v>
       </c>
@@ -6815,7 +6813,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="59" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="2:7" ht="18" customHeight="1">
       <c r="B59" t="s">
         <v>105</v>
       </c>
@@ -6833,7 +6831,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="60" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="2:7" ht="18" customHeight="1">
       <c r="B60" t="s">
         <v>190</v>
       </c>
@@ -6851,7 +6849,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="61" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="2:7" ht="18" customHeight="1">
       <c r="B61" t="s">
         <v>84</v>
       </c>
@@ -6869,7 +6867,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="62" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="2:7" ht="18" customHeight="1">
       <c r="B62" t="s">
         <v>96</v>
       </c>
@@ -6887,7 +6885,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="63" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="2:7" ht="18" customHeight="1">
       <c r="B63" t="s">
         <v>96</v>
       </c>
@@ -6905,7 +6903,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="64" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="2:7" ht="18" customHeight="1">
       <c r="B64" t="s">
         <v>87</v>
       </c>
@@ -6923,7 +6921,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="65" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:7" ht="18" customHeight="1">
       <c r="B65" t="s">
         <v>201</v>
       </c>
@@ -6941,7 +6939,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="66" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:7" ht="18" customHeight="1">
       <c r="B66" t="s">
         <v>204</v>
       </c>
@@ -6961,7 +6959,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="67" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:7" ht="18" customHeight="1">
       <c r="B67" t="s">
         <v>207</v>
       </c>
@@ -6981,7 +6979,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="68" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:7" ht="18" customHeight="1">
       <c r="B68" t="s">
         <v>210</v>
       </c>
@@ -7001,7 +6999,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="69" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:7" ht="18" customHeight="1">
       <c r="B69" t="s">
         <v>207</v>
       </c>
@@ -7021,7 +7019,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="70" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:7" ht="18" customHeight="1">
       <c r="B70" t="s">
         <v>84</v>
       </c>
@@ -7041,7 +7039,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="71" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:7" ht="18" customHeight="1">
       <c r="B71" t="s">
         <v>135</v>
       </c>
@@ -7061,7 +7059,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="72" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:7" ht="18" customHeight="1">
       <c r="B72" t="s">
         <v>151</v>
       </c>
@@ -7081,7 +7079,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="73" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:7" ht="18" customHeight="1">
       <c r="B73" t="s">
         <v>117</v>
       </c>
@@ -7101,7 +7099,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="74" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:7" ht="18" customHeight="1">
       <c r="B74" t="s">
         <v>222</v>
       </c>
@@ -7119,7 +7117,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="75" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:7" ht="18" customHeight="1">
       <c r="B75" t="s">
         <v>225</v>
       </c>
@@ -7139,7 +7137,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="76" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:7" ht="18" customHeight="1">
       <c r="B76" t="s">
         <v>222</v>
       </c>
@@ -7159,7 +7157,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="77" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:7" ht="18" customHeight="1">
       <c r="B77" t="s">
         <v>230</v>
       </c>
@@ -7179,7 +7177,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="78" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="2:7" ht="18" customHeight="1">
       <c r="B78" t="s">
         <v>151</v>
       </c>
@@ -7197,7 +7195,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="79" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:7" ht="18" customHeight="1">
       <c r="B79" t="s">
         <v>210</v>
       </c>
@@ -7215,7 +7213,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="80" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:7" ht="18" customHeight="1">
       <c r="B80" t="s">
         <v>105</v>
       </c>
@@ -7235,7 +7233,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="81" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="2:7" ht="18" customHeight="1">
       <c r="B81" t="s">
         <v>105</v>
       </c>
@@ -7253,7 +7251,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="82" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="2:7" ht="18" customHeight="1">
       <c r="B82" t="s">
         <v>240</v>
       </c>
@@ -7273,7 +7271,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="83" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="2:7" ht="18" customHeight="1">
       <c r="B83" t="s">
         <v>166</v>
       </c>
@@ -7293,7 +7291,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="84" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="2:7" ht="18" customHeight="1">
       <c r="B84" t="s">
         <v>34</v>
       </c>
@@ -7311,7 +7309,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="85" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="2:7" ht="18" customHeight="1">
       <c r="B85" t="s">
         <v>135</v>
       </c>
@@ -7331,7 +7329,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="86" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="2:7" ht="18" customHeight="1">
       <c r="B86" t="s">
         <v>249</v>
       </c>
@@ -7351,7 +7349,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="87" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="2:7" ht="18" customHeight="1">
       <c r="B87" t="s">
         <v>252</v>
       </c>
@@ -7371,7 +7369,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="88" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="2:7" ht="18" customHeight="1">
       <c r="B88" t="s">
         <v>105</v>
       </c>
@@ -7389,7 +7387,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="89" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="2:7" ht="18" customHeight="1">
       <c r="B89" t="s">
         <v>257</v>
       </c>
@@ -7409,7 +7407,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="90" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="2:7" ht="18" customHeight="1">
       <c r="B90" t="s">
         <v>58</v>
       </c>
@@ -7427,7 +7425,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="91" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="2:7" ht="18" customHeight="1">
       <c r="B91" t="s">
         <v>262</v>
       </c>
@@ -7447,7 +7445,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="92" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="2:7" ht="18" customHeight="1">
       <c r="B92" t="s">
         <v>105</v>
       </c>
@@ -7465,7 +7463,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="93" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="2:7" ht="18" customHeight="1">
       <c r="B93" t="s">
         <v>81</v>
       </c>
@@ -7485,7 +7483,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="94" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="94" spans="2:7" ht="18" customHeight="1">
       <c r="B94" t="s">
         <v>190</v>
       </c>
@@ -7503,7 +7501,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="95" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="95" spans="2:7" ht="18" customHeight="1">
       <c r="B95" t="s">
         <v>81</v>
       </c>
@@ -7521,7 +7519,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="96" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="96" spans="2:7" ht="18" customHeight="1">
       <c r="B96" t="s">
         <v>166</v>
       </c>
@@ -7541,7 +7539,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="97" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="2:7" ht="18" customHeight="1">
       <c r="B97" t="s">
         <v>274</v>
       </c>
@@ -7559,7 +7557,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="98" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="98" spans="2:7" ht="18" customHeight="1">
       <c r="B98" t="s">
         <v>277</v>
       </c>
@@ -7579,7 +7577,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="99" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="99" spans="2:7" ht="18" customHeight="1">
       <c r="B99" t="s">
         <v>277</v>
       </c>
@@ -7599,7 +7597,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="100" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="100" spans="2:7" ht="18" customHeight="1">
       <c r="B100" t="s">
         <v>281</v>
       </c>
@@ -7619,7 +7617,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="101" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="2:7" ht="18" customHeight="1">
       <c r="B101" t="s">
         <v>129</v>
       </c>
@@ -7639,7 +7637,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="102" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="2:7" ht="18" customHeight="1">
       <c r="B102" t="s">
         <v>129</v>
       </c>
@@ -7657,7 +7655,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="103" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="2:7" ht="18" customHeight="1">
       <c r="B103" t="s">
         <v>281</v>
       </c>
@@ -7675,7 +7673,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="104" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="2:7" ht="18" customHeight="1">
       <c r="B104" t="s">
         <v>290</v>
       </c>
@@ -7693,7 +7691,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="105" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="2:7" ht="18" customHeight="1">
       <c r="B105" t="s">
         <v>105</v>
       </c>
@@ -7711,7 +7709,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="106" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="106" spans="2:7" ht="18" customHeight="1">
       <c r="B106" t="s">
         <v>204</v>
       </c>
@@ -7729,7 +7727,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="107" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="107" spans="2:7" ht="18" customHeight="1">
       <c r="B107" t="s">
         <v>297</v>
       </c>
@@ -7749,7 +7747,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="108" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="108" spans="2:7" ht="18" customHeight="1">
       <c r="B108" t="s">
         <v>300</v>
       </c>
@@ -7766,7 +7764,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="109" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="109" spans="2:7" ht="18" customHeight="1">
       <c r="B109" t="s">
         <v>105</v>
       </c>
@@ -7783,7 +7781,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="110" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="110" spans="2:7" ht="18" customHeight="1">
       <c r="B110" t="s">
         <v>230</v>
       </c>
@@ -7803,7 +7801,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="111" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="111" spans="2:7" ht="18" customHeight="1">
       <c r="B111" t="s">
         <v>308</v>
       </c>
@@ -7820,7 +7818,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="112" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="112" spans="2:7" ht="18" customHeight="1">
       <c r="B112" t="s">
         <v>204</v>
       </c>
@@ -7837,7 +7835,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="113" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="113" spans="2:7" ht="18" customHeight="1">
       <c r="B113" t="s">
         <v>313</v>
       </c>
@@ -7854,7 +7852,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="114" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="114" spans="2:7" ht="18" customHeight="1">
       <c r="B114" t="s">
         <v>84</v>
       </c>
@@ -7871,7 +7869,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="115" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="115" spans="2:7" ht="18" customHeight="1">
       <c r="B115" t="s">
         <v>163</v>
       </c>
@@ -7888,7 +7886,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="116" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="116" spans="2:7" ht="18" customHeight="1">
       <c r="B116" t="s">
         <v>320</v>
       </c>
@@ -7905,7 +7903,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="117" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="117" spans="2:7" ht="18" customHeight="1">
       <c r="B117" t="s">
         <v>96</v>
       </c>
@@ -7922,7 +7920,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="118" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="118" spans="2:7" ht="18" customHeight="1">
       <c r="B118" t="s">
         <v>151</v>
       </c>
@@ -7939,7 +7937,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="119" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="119" spans="2:7" ht="18" customHeight="1">
       <c r="B119" t="s">
         <v>327</v>
       </c>
@@ -7959,7 +7957,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="120" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="120" spans="2:7" ht="18" customHeight="1">
       <c r="B120" t="s">
         <v>132</v>
       </c>
@@ -7976,7 +7974,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="121" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="121" spans="2:7" ht="18" customHeight="1">
       <c r="B121" t="s">
         <v>132</v>
       </c>
@@ -7996,7 +7994,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="122" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="122" spans="2:7" ht="18" customHeight="1">
       <c r="B122" t="s">
         <v>132</v>
       </c>
@@ -8016,7 +8014,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="123" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="123" spans="2:7" ht="18" customHeight="1">
       <c r="B123" t="s">
         <v>132</v>
       </c>
@@ -8033,7 +8031,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="124" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="124" spans="2:7" ht="18" customHeight="1">
       <c r="B124" t="s">
         <v>240</v>
       </c>
@@ -8053,7 +8051,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="125" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="125" spans="2:7" ht="18" customHeight="1">
       <c r="B125" t="s">
         <v>129</v>
       </c>
@@ -8070,7 +8068,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="126" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="126" spans="2:7" ht="18" customHeight="1">
       <c r="B126" t="s">
         <v>341</v>
       </c>
@@ -8087,7 +8085,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="127" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="127" spans="2:7" ht="18" customHeight="1">
       <c r="B127" t="s">
         <v>344</v>
       </c>
@@ -8104,7 +8102,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="128" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="128" spans="2:7" ht="18" customHeight="1">
       <c r="B128" t="s">
         <v>105</v>
       </c>
@@ -8121,7 +8119,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="129" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="129" spans="2:7" ht="18" customHeight="1">
       <c r="B129" t="s">
         <v>112</v>
       </c>
@@ -8141,7 +8139,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="130" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="130" spans="2:7" ht="18" customHeight="1">
       <c r="B130" t="s">
         <v>166</v>
       </c>
@@ -8161,7 +8159,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="131" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="131" spans="2:7" ht="18" customHeight="1">
       <c r="B131" t="s">
         <v>204</v>
       </c>
@@ -8178,7 +8176,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="132" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="132" spans="2:7" ht="18" customHeight="1">
       <c r="B132" t="s">
         <v>274</v>
       </c>
@@ -8195,7 +8193,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="133" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="133" spans="2:7" ht="18" customHeight="1">
       <c r="B133" t="s">
         <v>135</v>
       </c>
@@ -8215,7 +8213,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="134" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="134" spans="2:7" ht="18" customHeight="1">
       <c r="B134" t="s">
         <v>42</v>
       </c>
@@ -8232,7 +8230,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="135" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="135" spans="2:7" ht="18" customHeight="1">
       <c r="B135" t="s">
         <v>73</v>
       </c>
@@ -8249,7 +8247,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="136" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="136" spans="2:7" ht="18" customHeight="1">
       <c r="B136" t="s">
         <v>362</v>
       </c>
@@ -8269,7 +8267,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="137" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="137" spans="2:7" ht="18" customHeight="1">
       <c r="B137" t="s">
         <v>362</v>
       </c>
@@ -8289,7 +8287,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="138" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="138" spans="2:7" ht="18" customHeight="1">
       <c r="B138" t="s">
         <v>67</v>
       </c>
@@ -8306,7 +8304,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="139" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="139" spans="2:7" ht="18" customHeight="1">
       <c r="B139" t="s">
         <v>369</v>
       </c>
@@ -8323,7 +8321,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="140" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="140" spans="2:7" ht="18" customHeight="1">
       <c r="B140" t="s">
         <v>297</v>
       </c>
@@ -8343,7 +8341,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="141" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="141" spans="2:7" ht="18" customHeight="1">
       <c r="B141" t="s">
         <v>327</v>
       </c>
@@ -8363,7 +8361,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="142" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="142" spans="2:7" ht="18" customHeight="1">
       <c r="B142" t="s">
         <v>105</v>
       </c>
@@ -8380,7 +8378,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="143" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="143" spans="2:7" ht="18" customHeight="1">
       <c r="B143" t="s">
         <v>96</v>
       </c>
@@ -8397,7 +8395,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="144" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="144" spans="2:7" ht="18" customHeight="1">
       <c r="B144" t="s">
         <v>73</v>
       </c>
@@ -8414,7 +8412,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="145" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="145" spans="2:7" ht="18" customHeight="1">
       <c r="B145" t="s">
         <v>117</v>
       </c>
@@ -8431,7 +8429,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="146" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="146" spans="2:7" ht="18" customHeight="1">
       <c r="B146" t="s">
         <v>320</v>
       </c>
@@ -8448,7 +8446,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="147" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="147" spans="2:7" ht="18" customHeight="1">
       <c r="B147" t="s">
         <v>274</v>
       </c>
@@ -8465,7 +8463,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="148" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="148" spans="2:7" ht="18" customHeight="1">
       <c r="B148" t="s">
         <v>151</v>
       </c>
@@ -8482,7 +8480,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="149" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="149" spans="2:7" ht="18" customHeight="1">
       <c r="B149" t="s">
         <v>390</v>
       </c>
@@ -8499,7 +8497,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="150" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="150" spans="2:7" ht="18" customHeight="1">
       <c r="B150" t="s">
         <v>313</v>
       </c>
@@ -8516,7 +8514,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="151" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="151" spans="2:7" ht="18" customHeight="1">
       <c r="B151" t="s">
         <v>262</v>
       </c>
@@ -8533,7 +8531,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="152" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="152" spans="2:7" ht="18" customHeight="1">
       <c r="B152" t="s">
         <v>274</v>
       </c>
@@ -8550,7 +8548,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="153" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="153" spans="2:7" ht="18" customHeight="1">
       <c r="B153" t="s">
         <v>171</v>
       </c>
@@ -8567,7 +8565,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="154" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="154" spans="2:7" ht="18" customHeight="1">
       <c r="B154" t="s">
         <v>401</v>
       </c>
@@ -8584,7 +8582,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="155" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="155" spans="2:7" ht="18" customHeight="1">
       <c r="B155" t="s">
         <v>87</v>
       </c>
@@ -8601,7 +8599,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="156" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="156" spans="2:7" ht="18" customHeight="1">
       <c r="B156" t="s">
         <v>320</v>
       </c>
@@ -8618,7 +8616,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="157" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="157" spans="2:7" ht="18" customHeight="1">
       <c r="B157" t="s">
         <v>96</v>
       </c>
@@ -8638,7 +8636,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="158" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="158" spans="2:7" ht="18" customHeight="1">
       <c r="B158" t="s">
         <v>87</v>
       </c>
@@ -8656,7 +8654,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="159" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="159" spans="2:7" ht="18" customHeight="1">
       <c r="B159" t="s">
         <v>412</v>
       </c>
@@ -8673,7 +8671,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="160" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="160" spans="2:7" ht="18" customHeight="1">
       <c r="B160" t="s">
         <v>415</v>
       </c>
@@ -8690,7 +8688,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="161" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="161" spans="2:7" ht="18" customHeight="1">
       <c r="B161" t="s">
         <v>274</v>
       </c>
@@ -8707,7 +8705,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="162" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="162" spans="2:7" ht="18" customHeight="1">
       <c r="B162" t="s">
         <v>240</v>
       </c>
@@ -8727,7 +8725,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="163" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="163" spans="2:7" ht="18" customHeight="1">
       <c r="B163" t="s">
         <v>421</v>
       </c>
@@ -8744,7 +8742,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="164" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="164" spans="2:7" ht="18" customHeight="1">
       <c r="B164" t="s">
         <v>151</v>
       </c>
@@ -8761,7 +8759,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="165" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="165" spans="2:7" ht="18" customHeight="1">
       <c r="B165" t="s">
         <v>49</v>
       </c>
@@ -8778,7 +8776,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="166" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="166" spans="2:7" ht="18" customHeight="1">
       <c r="B166" t="s">
         <v>207</v>
       </c>
@@ -8798,7 +8796,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="167" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="167" spans="2:7" ht="18" customHeight="1">
       <c r="B167" t="s">
         <v>42</v>
       </c>
@@ -8815,7 +8813,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="168" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="168" spans="2:7" ht="18" customHeight="1">
       <c r="B168" t="s">
         <v>432</v>
       </c>
@@ -8832,7 +8830,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="169" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="169" spans="2:7" ht="18" customHeight="1">
       <c r="B169" t="s">
         <v>435</v>
       </c>
@@ -8849,7 +8847,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="170" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="170" spans="2:7" ht="18" customHeight="1">
       <c r="B170" t="s">
         <v>438</v>
       </c>
@@ -8866,7 +8864,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="171" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="171" spans="2:7" ht="18" customHeight="1">
       <c r="B171" t="s">
         <v>441</v>
       </c>
@@ -8883,7 +8881,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="172" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="172" spans="2:7" ht="18" customHeight="1">
       <c r="B172" t="s">
         <v>179</v>
       </c>
@@ -8900,7 +8898,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="173" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="173" spans="2:7" ht="18" customHeight="1">
       <c r="B173" t="s">
         <v>78</v>
       </c>
@@ -8917,7 +8915,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="174" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="174" spans="2:7" ht="18" customHeight="1">
       <c r="B174" t="s">
         <v>448</v>
       </c>
@@ -8934,7 +8932,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="175" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="175" spans="2:7" ht="18" customHeight="1">
       <c r="B175" t="s">
         <v>84</v>
       </c>
@@ -8951,7 +8949,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="176" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="176" spans="2:7" ht="18" customHeight="1">
       <c r="B176" t="s">
         <v>252</v>
       </c>
@@ -8968,7 +8966,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="177" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="177" spans="2:7" ht="18" customHeight="1">
       <c r="B177" t="s">
         <v>87</v>
       </c>
@@ -8985,7 +8983,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="178" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="178" spans="2:7" ht="18" customHeight="1">
       <c r="B178" t="s">
         <v>132</v>
       </c>
@@ -9002,7 +9000,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="179" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="179" spans="2:7" ht="18" customHeight="1">
       <c r="B179" t="s">
         <v>257</v>
       </c>
@@ -9019,7 +9017,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="180" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="180" spans="2:7" ht="18" customHeight="1">
       <c r="B180" t="s">
         <v>222</v>
       </c>
@@ -9036,7 +9034,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="181" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="181" spans="2:7" ht="18" customHeight="1">
       <c r="B181" t="s">
         <v>462</v>
       </c>
@@ -9053,7 +9051,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="182" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="182" spans="2:7" ht="18" customHeight="1">
       <c r="B182" t="s">
         <v>210</v>
       </c>
@@ -9070,7 +9068,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="183" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="183" spans="2:7" ht="18" customHeight="1">
       <c r="B183" t="s">
         <v>415</v>
       </c>
@@ -9087,7 +9085,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="184" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="184" spans="2:7" ht="18" customHeight="1">
       <c r="B184" t="s">
         <v>52</v>
       </c>
@@ -9104,7 +9102,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="185" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="185" spans="2:7" ht="18" customHeight="1">
       <c r="B185" t="s">
         <v>129</v>
       </c>
@@ -9121,7 +9119,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="186" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="186" spans="2:7" ht="18" customHeight="1">
       <c r="B186" t="s">
         <v>87</v>
       </c>
@@ -9138,7 +9136,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="187" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="187" spans="2:7" ht="18" customHeight="1">
       <c r="B187" t="s">
         <v>274</v>
       </c>
@@ -9155,7 +9153,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="188" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="188" spans="2:7" ht="18" customHeight="1">
       <c r="B188" t="s">
         <v>441</v>
       </c>
@@ -9172,7 +9170,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="189" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="189" spans="2:7" ht="18" customHeight="1">
       <c r="B189" t="s">
         <v>120</v>
       </c>
@@ -9189,7 +9187,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="190" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="190" spans="2:7" ht="18" customHeight="1">
       <c r="B190" t="s">
         <v>129</v>
       </c>
@@ -9206,7 +9204,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="191" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="191" spans="2:7" ht="18" customHeight="1">
       <c r="B191" t="s">
         <v>390</v>
       </c>
@@ -9223,7 +9221,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="192" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="192" spans="2:7" ht="18" customHeight="1">
       <c r="B192" t="s">
         <v>204</v>
       </c>
@@ -9240,7 +9238,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="193" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="193" spans="2:7" ht="18" customHeight="1">
       <c r="B193" t="s">
         <v>401</v>
       </c>
@@ -9257,7 +9255,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="194" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="194" spans="2:7" ht="18" customHeight="1">
       <c r="B194" t="s">
         <v>435</v>
       </c>
@@ -9274,7 +9272,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="195" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="195" spans="2:7" ht="18" customHeight="1">
       <c r="B195" t="s">
         <v>129</v>
       </c>
@@ -9291,7 +9289,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="196" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="196" spans="2:7" ht="18" customHeight="1">
       <c r="B196" t="s">
         <v>492</v>
       </c>
@@ -9308,7 +9306,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="197" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="197" spans="2:7" ht="18" customHeight="1">
       <c r="B197" t="s">
         <v>252</v>
       </c>
@@ -9325,7 +9323,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="198" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="198" spans="2:7" ht="18" customHeight="1">
       <c r="B198" t="s">
         <v>46</v>
       </c>
@@ -9342,7 +9340,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="199" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="199" spans="2:7" ht="18" customHeight="1">
       <c r="B199" t="s">
         <v>55</v>
       </c>
@@ -9359,7 +9357,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="200" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="200" spans="2:7" ht="18" customHeight="1">
       <c r="B200" t="s">
         <v>132</v>
       </c>
@@ -9376,7 +9374,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="201" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="201" spans="2:7" ht="18" customHeight="1">
       <c r="B201" t="s">
         <v>369</v>
       </c>
@@ -9393,7 +9391,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="202" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="202" spans="2:7" ht="18" customHeight="1">
       <c r="B202" t="s">
         <v>505</v>
       </c>
@@ -9410,7 +9408,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="203" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="203" spans="2:7" ht="18" customHeight="1">
       <c r="B203" t="s">
         <v>129</v>
       </c>
@@ -9427,7 +9425,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="204" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="204" spans="2:7" ht="18" customHeight="1">
       <c r="B204" t="s">
         <v>510</v>
       </c>
@@ -9447,7 +9445,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="205" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="205" spans="2:7" ht="18" customHeight="1">
       <c r="B205" t="s">
         <v>257</v>
       </c>
@@ -9464,7 +9462,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="206" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="206" spans="2:7" ht="18" customHeight="1">
       <c r="B206" t="s">
         <v>38</v>
       </c>
@@ -9481,7 +9479,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="207" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="207" spans="2:7" ht="18" customHeight="1">
       <c r="B207" t="s">
         <v>204</v>
       </c>
@@ -9498,7 +9496,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="208" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="208" spans="2:7" ht="18" customHeight="1">
       <c r="B208" t="s">
         <v>171</v>
       </c>
@@ -9515,7 +9513,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="209" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="209" spans="2:7" ht="18" customHeight="1">
       <c r="B209" t="s">
         <v>341</v>
       </c>
@@ -9532,7 +9530,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="210" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="210" spans="2:7" ht="18" customHeight="1">
       <c r="B210" t="s">
         <v>64</v>
       </c>
@@ -9549,7 +9547,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="211" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="211" spans="2:7" ht="18" customHeight="1">
       <c r="B211" t="s">
         <v>524</v>
       </c>
@@ -9566,7 +9564,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="212" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="212" spans="2:7" ht="18" customHeight="1">
       <c r="B212" t="s">
         <v>120</v>
       </c>
@@ -9583,7 +9581,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="213" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="213" spans="2:7" ht="18" customHeight="1">
       <c r="B213" t="s">
         <v>84</v>
       </c>
@@ -9600,7 +9598,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="214" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="214" spans="2:7" ht="18" customHeight="1">
       <c r="B214" t="s">
         <v>163</v>
       </c>
@@ -9617,7 +9615,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="215" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="215" spans="2:7" ht="18" customHeight="1">
       <c r="B215" t="s">
         <v>96</v>
       </c>
@@ -9637,7 +9635,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="216" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="216" spans="2:7" ht="18" customHeight="1">
       <c r="B216" t="s">
         <v>129</v>
       </c>
@@ -9654,7 +9652,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="217" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="217" spans="2:7" ht="18" customHeight="1">
       <c r="B217" t="s">
         <v>204</v>
       </c>
@@ -9671,7 +9669,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="218" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="218" spans="2:7" ht="18" customHeight="1">
       <c r="B218" t="s">
         <v>252</v>
       </c>
@@ -9688,7 +9686,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="219" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="219" spans="2:7" ht="18" customHeight="1">
       <c r="B219" t="s">
         <v>135</v>
       </c>
@@ -9705,7 +9703,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="220" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="220" spans="2:7" ht="18" customHeight="1">
       <c r="B220" t="s">
         <v>262</v>
       </c>
@@ -9722,7 +9720,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="221" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="221" spans="2:7" ht="18" customHeight="1">
       <c r="B221" t="s">
         <v>300</v>
       </c>
@@ -9739,7 +9737,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="222" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="222" spans="2:7" ht="18" customHeight="1">
       <c r="B222" t="s">
         <v>105</v>
       </c>
@@ -9756,7 +9754,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="223" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="223" spans="2:7" ht="18" customHeight="1">
       <c r="B223" t="s">
         <v>105</v>
       </c>
@@ -9773,7 +9771,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="224" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="224" spans="2:7" ht="18" customHeight="1">
       <c r="B224" t="s">
         <v>281</v>
       </c>
@@ -9790,7 +9788,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="225" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="225" spans="2:7" ht="18" customHeight="1">
       <c r="B225" t="s">
         <v>132</v>
       </c>
@@ -9807,7 +9805,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="226" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="226" spans="2:7" ht="18" customHeight="1">
       <c r="B226" t="s">
         <v>151</v>
       </c>
@@ -9824,7 +9822,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="227" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="227" spans="2:7" ht="18" customHeight="1">
       <c r="B227" t="s">
         <v>257</v>
       </c>
@@ -9841,7 +9839,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="228" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="228" spans="2:7" ht="18" customHeight="1">
       <c r="B228" t="s">
         <v>156</v>
       </c>
@@ -9858,7 +9856,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="229" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="229" spans="2:7" ht="18" customHeight="1">
       <c r="B229" t="s">
         <v>176</v>
       </c>
@@ -9875,7 +9873,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="230" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="230" spans="2:7" ht="18" customHeight="1">
       <c r="B230" t="s">
         <v>225</v>
       </c>
@@ -9892,7 +9890,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="231" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="231" spans="2:7" ht="18" customHeight="1">
       <c r="B231" t="s">
         <v>448</v>
       </c>
@@ -9909,7 +9907,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="232" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="232" spans="2:7" ht="18" customHeight="1">
       <c r="B232" t="s">
         <v>129</v>
       </c>
@@ -9926,7 +9924,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="233" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="233" spans="2:7" ht="18" customHeight="1">
       <c r="B233" t="s">
         <v>567</v>
       </c>
@@ -9943,7 +9941,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="234" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="234" spans="2:7" ht="18" customHeight="1">
       <c r="B234" t="s">
         <v>87</v>
       </c>
@@ -9960,7 +9958,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="235" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="235" spans="2:7" ht="18" customHeight="1">
       <c r="B235" t="s">
         <v>112</v>
       </c>
@@ -9980,7 +9978,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="236" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="236" spans="2:7" ht="18" customHeight="1">
       <c r="B236" t="s">
         <v>277</v>
       </c>
@@ -10000,7 +9998,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="237" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="237" spans="2:7" ht="18" customHeight="1">
       <c r="B237" t="s">
         <v>49</v>
       </c>
@@ -10017,7 +10015,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="238" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="238" spans="2:7" ht="18" customHeight="1">
       <c r="B238" t="s">
         <v>578</v>
       </c>
@@ -10034,7 +10032,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="239" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="239" spans="2:7" ht="18" customHeight="1">
       <c r="B239" t="s">
         <v>166</v>
       </c>
@@ -10051,7 +10049,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="240" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="240" spans="2:7" ht="18" customHeight="1">
       <c r="B240" t="s">
         <v>135</v>
       </c>
@@ -10071,7 +10069,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="241" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="241" spans="2:7" ht="18" customHeight="1">
       <c r="B241" t="s">
         <v>176</v>
       </c>
@@ -10088,7 +10086,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="242" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="242" spans="2:7" ht="18" customHeight="1">
       <c r="B242" t="s">
         <v>585</v>
       </c>
@@ -10105,10 +10103,10 @@
         <v>586</v>
       </c>
       <c r="G242" t="s">
-        <v>634</v>
-      </c>
-    </row>
-    <row r="243" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="243" spans="2:7" ht="18" customHeight="1">
       <c r="B243" t="s">
         <v>204</v>
       </c>
@@ -10119,13 +10117,13 @@
         <v>45134</v>
       </c>
       <c r="F243" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="G243" t="s">
-        <v>588</v>
-      </c>
-    </row>
-    <row r="244" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="244" spans="2:7" ht="18" customHeight="1">
       <c r="B244" t="s">
         <v>249</v>
       </c>
@@ -10136,13 +10134,13 @@
         <v>45148</v>
       </c>
       <c r="F244" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="G244" t="s">
-        <v>590</v>
-      </c>
-    </row>
-    <row r="245" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="245" spans="2:7" ht="18" customHeight="1">
       <c r="B245" t="s">
         <v>274</v>
       </c>
@@ -10153,13 +10151,13 @@
         <v>45148</v>
       </c>
       <c r="F245" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="G245" t="s">
-        <v>592</v>
-      </c>
-    </row>
-    <row r="246" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="246" spans="2:7" ht="18" customHeight="1">
       <c r="B246" t="s">
         <v>432</v>
       </c>
@@ -10170,13 +10168,13 @@
         <v>45152</v>
       </c>
       <c r="F246" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="G246" t="s">
-        <v>594</v>
-      </c>
-    </row>
-    <row r="247" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="247" spans="2:7" ht="18" customHeight="1">
       <c r="B247" t="s">
         <v>129</v>
       </c>
@@ -10187,13 +10185,13 @@
         <v>45153</v>
       </c>
       <c r="F247" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="G247" t="s">
-        <v>596</v>
-      </c>
-    </row>
-    <row r="248" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="248" spans="2:7" ht="18" customHeight="1">
       <c r="B248" t="s">
         <v>144</v>
       </c>
@@ -10207,13 +10205,13 @@
         <v>45161</v>
       </c>
       <c r="F248" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="G248" t="s">
-        <v>598</v>
-      </c>
-    </row>
-    <row r="249" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="249" spans="2:7" ht="18" customHeight="1">
       <c r="B249" t="s">
         <v>166</v>
       </c>
@@ -10227,13 +10225,13 @@
         <v>45167</v>
       </c>
       <c r="F249" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="G249" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="250" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="250" spans="2:7" ht="18" customHeight="1">
       <c r="B250" t="s">
         <v>190</v>
       </c>
@@ -10244,13 +10242,13 @@
         <v>45168</v>
       </c>
       <c r="F250" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="G250" s="18" t="s">
-        <v>602</v>
-      </c>
-    </row>
-    <row r="251" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="251" spans="2:7" ht="18" customHeight="1">
       <c r="B251" t="s">
         <v>390</v>
       </c>
@@ -10261,13 +10259,13 @@
         <v>45168</v>
       </c>
       <c r="F251" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="G251" s="18" t="s">
-        <v>604</v>
-      </c>
-    </row>
-    <row r="252" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="252" spans="2:7" ht="18" customHeight="1">
       <c r="B252" t="s">
         <v>435</v>
       </c>
@@ -10278,13 +10276,13 @@
         <v>45168</v>
       </c>
       <c r="F252" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="G252" t="s">
-        <v>606</v>
-      </c>
-    </row>
-    <row r="253" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="253" spans="2:7" ht="18" customHeight="1">
       <c r="B253" t="s">
         <v>510</v>
       </c>
@@ -10298,13 +10296,13 @@
         <v>45168</v>
       </c>
       <c r="F253" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="G253" s="18" t="s">
-        <v>608</v>
-      </c>
-    </row>
-    <row r="254" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="254" spans="2:7" ht="18" customHeight="1">
       <c r="B254" t="s">
         <v>341</v>
       </c>
@@ -10315,13 +10313,13 @@
         <v>45169</v>
       </c>
       <c r="F254" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="G254" t="s">
-        <v>610</v>
-      </c>
-    </row>
-    <row r="255" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="255" spans="2:7" ht="18" customHeight="1">
       <c r="B255" t="s">
         <v>58</v>
       </c>
@@ -10332,13 +10330,13 @@
         <v>45177</v>
       </c>
       <c r="F255" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="G255" t="s">
-        <v>612</v>
-      </c>
-    </row>
-    <row r="256" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="256" spans="2:7" ht="18" customHeight="1">
       <c r="B256" t="s">
         <v>277</v>
       </c>
@@ -10352,13 +10350,13 @@
         <v>45183</v>
       </c>
       <c r="F256" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="G256" s="18" t="s">
-        <v>614</v>
-      </c>
-    </row>
-    <row r="257" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="257" spans="2:7" ht="18" customHeight="1">
       <c r="B257" t="s">
         <v>320</v>
       </c>
@@ -10369,13 +10367,13 @@
         <v>45186</v>
       </c>
       <c r="F257" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="G257" s="18" t="s">
-        <v>616</v>
-      </c>
-    </row>
-    <row r="258" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="258" spans="2:7" ht="18" customHeight="1">
       <c r="B258" t="s">
         <v>58</v>
       </c>
@@ -10386,13 +10384,13 @@
         <v>45194</v>
       </c>
       <c r="F258" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="G258" s="18" t="s">
-        <v>618</v>
-      </c>
-    </row>
-    <row r="259" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="259" spans="2:7" ht="18" customHeight="1">
       <c r="B259" t="s">
         <v>156</v>
       </c>
@@ -10403,13 +10401,13 @@
         <v>45197</v>
       </c>
       <c r="F259" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="G259" s="18" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="260" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="260" spans="2:7" ht="18" customHeight="1">
       <c r="B260" t="s">
         <v>132</v>
       </c>
@@ -10420,15 +10418,15 @@
         <v>45198</v>
       </c>
       <c r="F260" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="G260" s="18" t="s">
-        <v>621</v>
-      </c>
-    </row>
-    <row r="261" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="261" spans="2:7" ht="18" customHeight="1">
       <c r="B261" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="D261" t="s">
         <v>39</v>
@@ -10437,13 +10435,13 @@
         <v>45198</v>
       </c>
       <c r="F261" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="G261" s="18" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="262" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="262" spans="2:7" ht="18" customHeight="1">
       <c r="B262" t="s">
         <v>204</v>
       </c>
@@ -10454,13 +10452,13 @@
         <v>45201</v>
       </c>
       <c r="F262" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="G262" t="s">
-        <v>626</v>
-      </c>
-    </row>
-    <row r="263" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="263" spans="2:7" ht="18" customHeight="1">
       <c r="B263" t="s">
         <v>401</v>
       </c>
@@ -10471,13 +10469,13 @@
         <v>45201</v>
       </c>
       <c r="F263" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="G263" s="18" t="s">
-        <v>628</v>
-      </c>
-    </row>
-    <row r="264" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="264" spans="2:7" ht="18" customHeight="1">
       <c r="B264" t="s">
         <v>176</v>
       </c>
@@ -10488,13 +10486,13 @@
         <v>45202</v>
       </c>
       <c r="F264" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="G264" s="18" t="s">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="265" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="265" spans="2:7" ht="18" customHeight="1">
       <c r="B265" t="s">
         <v>262</v>
       </c>
@@ -10505,13 +10503,13 @@
         <v>45203</v>
       </c>
       <c r="F265" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="G265" s="18" t="s">
-        <v>632</v>
-      </c>
-    </row>
-    <row r="266" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="266" spans="2:7" ht="18" customHeight="1">
       <c r="B266" t="s">
         <v>112</v>
       </c>
@@ -10525,13 +10523,13 @@
         <v>45203</v>
       </c>
       <c r="F266" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="G266" s="18" t="s">
-        <v>634</v>
-      </c>
-    </row>
-    <row r="267" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="267" spans="2:7" ht="18" customHeight="1">
       <c r="B267" t="s">
         <v>171</v>
       </c>
@@ -10549,7 +10547,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="268" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="268" spans="2:7" ht="18" customHeight="1">
       <c r="B268" t="s">
         <v>58</v>
       </c>
@@ -10566,7 +10564,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="269" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="269" spans="2:7" ht="18" customHeight="1">
       <c r="B269" t="s">
         <v>78</v>
       </c>
@@ -10583,7 +10581,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="270" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="270" spans="2:7" ht="18" customHeight="1">
       <c r="B270" t="s">
         <v>290</v>
       </c>
@@ -10600,7 +10598,7 @@
         <v>641</v>
       </c>
     </row>
-    <row r="271" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="271" spans="2:7" ht="18" customHeight="1">
       <c r="B271" t="s">
         <v>252</v>
       </c>
@@ -10617,7 +10615,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="272" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="272" spans="2:7" ht="18" customHeight="1">
       <c r="B272" t="s">
         <v>151</v>
       </c>
@@ -10634,7 +10632,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="273" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="273" spans="2:7" ht="18" customHeight="1">
       <c r="B273" t="s">
         <v>492</v>
       </c>
@@ -10651,7 +10649,7 @@
         <v>647</v>
       </c>
     </row>
-    <row r="274" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="274" spans="2:7" ht="18" customHeight="1">
       <c r="B274" t="s">
         <v>120</v>
       </c>
@@ -10668,7 +10666,7 @@
         <v>649</v>
       </c>
     </row>
-    <row r="275" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="275" spans="2:7" ht="18" customHeight="1">
       <c r="B275" t="s">
         <v>129</v>
       </c>
@@ -10685,7 +10683,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="276" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="276" spans="2:7" ht="18" customHeight="1">
       <c r="B276" t="s">
         <v>441</v>
       </c>
@@ -10702,7 +10700,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="277" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="277" spans="2:7" ht="18" customHeight="1">
       <c r="B277" t="s">
         <v>230</v>
       </c>
@@ -10719,7 +10717,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="278" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="278" spans="2:7" ht="18" customHeight="1">
       <c r="B278" t="s">
         <v>300</v>
       </c>
@@ -10736,7 +10734,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="279" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="279" spans="2:7" ht="18" customHeight="1">
       <c r="B279" t="s">
         <v>492</v>
       </c>
@@ -10753,7 +10751,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="280" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="280" spans="2:7" ht="18" customHeight="1">
       <c r="B280" t="s">
         <v>225</v>
       </c>
@@ -10770,7 +10768,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="281" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="281" spans="2:7" ht="18" customHeight="1">
       <c r="B281" t="s">
         <v>313</v>
       </c>
@@ -10787,9 +10785,9 @@
         <v>663</v>
       </c>
     </row>
-    <row r="282" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="282" spans="2:7" ht="18" customHeight="1">
       <c r="B282" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="D282" t="s">
         <v>39</v>
@@ -10804,7 +10802,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="283" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="283" spans="2:7" ht="18" customHeight="1">
       <c r="B283" t="s">
         <v>666</v>
       </c>
@@ -10821,7 +10819,7 @@
         <v>668</v>
       </c>
     </row>
-    <row r="284" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="284" spans="2:7" ht="18" customHeight="1">
       <c r="B284" t="s">
         <v>151</v>
       </c>
@@ -10838,7 +10836,7 @@
         <v>670</v>
       </c>
     </row>
-    <row r="285" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="285" spans="2:7" ht="18" customHeight="1">
       <c r="B285" t="s">
         <v>230</v>
       </c>
@@ -10856,7 +10854,7 @@
         <v>672</v>
       </c>
     </row>
-    <row r="286" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="286" spans="2:7" ht="18" customHeight="1">
       <c r="B286" t="s">
         <v>129</v>
       </c>
@@ -10873,7 +10871,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="287" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="287" spans="2:7" ht="18" customHeight="1">
       <c r="B287" t="s">
         <v>277</v>
       </c>
@@ -10893,7 +10891,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="288" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="288" spans="2:7" ht="18" customHeight="1">
       <c r="B288" t="s">
         <v>677</v>
       </c>
@@ -10913,7 +10911,7 @@
         <v>679</v>
       </c>
     </row>
-    <row r="289" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="289" spans="2:7" ht="18" customHeight="1">
       <c r="B289" t="s">
         <v>249</v>
       </c>
@@ -10930,7 +10928,7 @@
         <v>681</v>
       </c>
     </row>
-    <row r="290" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="290" spans="2:7" ht="18" customHeight="1">
       <c r="B290" t="s">
         <v>252</v>
       </c>
@@ -10948,7 +10946,7 @@
         <v>683</v>
       </c>
     </row>
-    <row r="291" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="291" spans="2:7" ht="18" customHeight="1">
       <c r="B291" t="s">
         <v>105</v>
       </c>
@@ -10966,7 +10964,7 @@
         <v>685</v>
       </c>
     </row>
-    <row r="292" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="292" spans="2:7" ht="18" customHeight="1">
       <c r="B292" t="s">
         <v>240</v>
       </c>
@@ -10986,7 +10984,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="293" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="293" spans="2:7" ht="18" customHeight="1">
       <c r="B293" t="s">
         <v>171</v>
       </c>
@@ -11003,7 +11001,7 @@
         <v>688</v>
       </c>
     </row>
-    <row r="294" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="294" spans="2:7" ht="18" customHeight="1">
       <c r="B294" t="s">
         <v>415</v>
       </c>
@@ -11020,7 +11018,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="295" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="295" spans="2:7" ht="18" customHeight="1">
       <c r="B295" t="s">
         <v>135</v>
       </c>
@@ -11040,7 +11038,7 @@
         <v>692</v>
       </c>
     </row>
-    <row r="296" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="296" spans="2:7" ht="18" customHeight="1">
       <c r="B296" t="s">
         <v>166</v>
       </c>
@@ -11060,7 +11058,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="297" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="297" spans="2:7" ht="18" customHeight="1">
       <c r="B297" t="s">
         <v>249</v>
       </c>
@@ -11078,7 +11076,7 @@
         <v>695</v>
       </c>
     </row>
-    <row r="298" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="298" spans="2:7" ht="18" customHeight="1">
       <c r="B298" t="s">
         <v>135</v>
       </c>
@@ -11098,7 +11096,7 @@
         <v>697</v>
       </c>
     </row>
-    <row r="299" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="299" spans="2:7" ht="18" customHeight="1">
       <c r="B299" t="s">
         <v>58</v>
       </c>
@@ -11116,7 +11114,7 @@
         <v>699</v>
       </c>
     </row>
-    <row r="300" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="300" spans="2:7" ht="18" customHeight="1">
       <c r="B300" t="s">
         <v>441</v>
       </c>
@@ -11134,7 +11132,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="301" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="301" spans="2:7" ht="18" customHeight="1">
       <c r="B301" t="s">
         <v>190</v>
       </c>
@@ -11151,7 +11149,7 @@
         <v>703</v>
       </c>
     </row>
-    <row r="302" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="302" spans="2:7" ht="18" customHeight="1">
       <c r="B302" t="s">
         <v>435</v>
       </c>
@@ -11169,7 +11167,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="303" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="303" spans="2:7" ht="18" customHeight="1">
       <c r="B303" t="s">
         <v>207</v>
       </c>
@@ -11189,7 +11187,7 @@
         <v>707</v>
       </c>
     </row>
-    <row r="304" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="304" spans="2:7" ht="18" customHeight="1">
       <c r="B304" t="s">
         <v>290</v>
       </c>
@@ -11206,7 +11204,7 @@
         <v>709</v>
       </c>
     </row>
-    <row r="305" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="305" spans="2:7" ht="18" customHeight="1">
       <c r="B305" t="s">
         <v>710</v>
       </c>
@@ -11223,7 +11221,7 @@
         <v>712</v>
       </c>
     </row>
-    <row r="306" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="306" spans="2:7" ht="18" customHeight="1">
       <c r="B306" t="s">
         <v>78</v>
       </c>
@@ -11241,7 +11239,7 @@
         <v>714</v>
       </c>
     </row>
-    <row r="307" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="307" spans="2:7" ht="18" customHeight="1">
       <c r="B307" t="s">
         <v>297</v>
       </c>
@@ -11261,7 +11259,7 @@
         <v>716</v>
       </c>
     </row>
-    <row r="308" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="308" spans="2:7" ht="18" customHeight="1">
       <c r="B308" t="s">
         <v>230</v>
       </c>
@@ -11279,7 +11277,7 @@
         <v>718</v>
       </c>
     </row>
-    <row r="309" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="309" spans="2:7" ht="18" customHeight="1">
       <c r="B309" t="s">
         <v>210</v>
       </c>
@@ -11296,7 +11294,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="310" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="310" spans="2:7" ht="18" customHeight="1">
       <c r="B310" t="s">
         <v>42</v>
       </c>
@@ -11313,7 +11311,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="311" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="311" spans="2:7" ht="18" customHeight="1">
       <c r="B311" t="s">
         <v>166</v>
       </c>
@@ -11333,7 +11331,7 @@
         <v>724</v>
       </c>
     </row>
-    <row r="312" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="312" spans="2:7" ht="18" customHeight="1">
       <c r="B312" t="s">
         <v>492</v>
       </c>
@@ -11353,7 +11351,7 @@
         <v>727</v>
       </c>
     </row>
-    <row r="313" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="313" spans="2:7" ht="18" customHeight="1">
       <c r="B313" t="s">
         <v>46</v>
       </c>
@@ -11373,7 +11371,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="314" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="314" spans="2:7" ht="18" customHeight="1">
       <c r="B314" t="s">
         <v>163</v>
       </c>
@@ -11393,7 +11391,7 @@
         <v>730</v>
       </c>
     </row>
-    <row r="315" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="315" spans="2:7" ht="18" customHeight="1">
       <c r="B315" t="s">
         <v>105</v>
       </c>
@@ -11413,7 +11411,7 @@
         <v>732</v>
       </c>
     </row>
-    <row r="316" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="316" spans="2:7" ht="18" customHeight="1">
       <c r="B316" t="s">
         <v>96</v>
       </c>
@@ -11433,7 +11431,7 @@
         <v>734</v>
       </c>
     </row>
-    <row r="317" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="317" spans="2:7" ht="18" customHeight="1">
       <c r="B317" t="s">
         <v>297</v>
       </c>
@@ -11453,7 +11451,7 @@
         <v>736</v>
       </c>
     </row>
-    <row r="318" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="318" spans="2:7" ht="18" customHeight="1">
       <c r="B318" t="s">
         <v>274</v>
       </c>
@@ -11473,9 +11471,9 @@
         <v>738</v>
       </c>
     </row>
-    <row r="319" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="319" spans="2:7" ht="18" customHeight="1">
       <c r="B319" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="C319" s="11">
         <v>229970</v>
@@ -11493,7 +11491,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="320" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="320" spans="2:7" ht="18" customHeight="1">
       <c r="B320" t="s">
         <v>741</v>
       </c>
@@ -11513,7 +11511,7 @@
         <v>743</v>
       </c>
     </row>
-    <row r="321" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="321" spans="2:7" ht="18" customHeight="1">
       <c r="B321" t="s">
         <v>129</v>
       </c>
@@ -11533,7 +11531,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="322" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="322" spans="2:7" ht="18" customHeight="1">
       <c r="B322" t="s">
         <v>132</v>
       </c>
@@ -11553,7 +11551,7 @@
         <v>747</v>
       </c>
     </row>
-    <row r="323" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="323" spans="2:7" ht="18" customHeight="1">
       <c r="B323" t="s">
         <v>87</v>
       </c>
@@ -11573,7 +11571,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="324" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="324" spans="2:7" ht="18" customHeight="1">
       <c r="B324" t="s">
         <v>151</v>
       </c>
@@ -11593,7 +11591,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="325" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="325" spans="2:7" ht="18" customHeight="1">
       <c r="B325" t="s">
         <v>166</v>
       </c>
@@ -11613,7 +11611,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="326" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="326" spans="2:7" ht="18" customHeight="1">
       <c r="B326" t="s">
         <v>666</v>
       </c>
@@ -11633,7 +11631,7 @@
         <v>752</v>
       </c>
     </row>
-    <row r="327" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="327" spans="2:7" ht="18" customHeight="1">
       <c r="B327" t="s">
         <v>415</v>
       </c>
@@ -11653,7 +11651,7 @@
         <v>754</v>
       </c>
     </row>
-    <row r="328" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="328" spans="2:7" ht="18" customHeight="1">
       <c r="B328" t="s">
         <v>415</v>
       </c>
@@ -11673,7 +11671,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="329" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="329" spans="2:7" ht="18" customHeight="1">
       <c r="B329" t="s">
         <v>176</v>
       </c>
@@ -11693,7 +11691,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="330" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="330" spans="2:7" ht="18" customHeight="1">
       <c r="B330" t="s">
         <v>341</v>
       </c>
@@ -11713,7 +11711,7 @@
         <v>759</v>
       </c>
     </row>
-    <row r="331" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="331" spans="2:7" ht="18" customHeight="1">
       <c r="B331" t="s">
         <v>58</v>
       </c>
@@ -11733,7 +11731,7 @@
         <v>761</v>
       </c>
     </row>
-    <row r="332" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="332" spans="2:7" ht="18" customHeight="1">
       <c r="B332" t="s">
         <v>84</v>
       </c>
@@ -11753,7 +11751,7 @@
         <v>763</v>
       </c>
     </row>
-    <row r="333" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="333" spans="2:7" ht="18" customHeight="1">
       <c r="B333" t="s">
         <v>163</v>
       </c>
@@ -11773,7 +11771,7 @@
         <v>730</v>
       </c>
     </row>
-    <row r="334" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="334" spans="2:7" ht="18" customHeight="1">
       <c r="B334" t="s">
         <v>105</v>
       </c>
@@ -11793,7 +11791,7 @@
         <v>766</v>
       </c>
     </row>
-    <row r="335" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="335" spans="2:7" ht="18" customHeight="1">
       <c r="B335" t="s">
         <v>240</v>
       </c>
@@ -11813,7 +11811,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="336" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="336" spans="2:7" ht="18" customHeight="1">
       <c r="B336" t="s">
         <v>117</v>
       </c>
@@ -11833,7 +11831,7 @@
         <v>769</v>
       </c>
     </row>
-    <row r="337" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="337" spans="2:7" ht="18" customHeight="1">
       <c r="B337" t="s">
         <v>78</v>
       </c>
@@ -11853,7 +11851,7 @@
         <v>771</v>
       </c>
     </row>
-    <row r="338" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="338" spans="2:7" ht="18" customHeight="1">
       <c r="B338" t="s">
         <v>210</v>
       </c>
@@ -11873,7 +11871,7 @@
         <v>773</v>
       </c>
     </row>
-    <row r="339" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="339" spans="2:7" ht="18" customHeight="1">
       <c r="B339" t="s">
         <v>73</v>
       </c>
@@ -11893,7 +11891,7 @@
         <v>775</v>
       </c>
     </row>
-    <row r="340" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="340" spans="2:7" ht="18" customHeight="1">
       <c r="B340" t="s">
         <v>171</v>
       </c>
@@ -11913,7 +11911,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="341" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="341" spans="2:7" ht="18" customHeight="1">
       <c r="B341" t="s">
         <v>344</v>
       </c>
@@ -11933,7 +11931,7 @@
         <v>778</v>
       </c>
     </row>
-    <row r="342" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="342" spans="2:7" ht="18" customHeight="1">
       <c r="B342" t="s">
         <v>401</v>
       </c>
@@ -11953,7 +11951,7 @@
         <v>780</v>
       </c>
     </row>
-    <row r="343" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="343" spans="2:7" ht="18" customHeight="1">
       <c r="B343" t="s">
         <v>96</v>
       </c>
@@ -11973,7 +11971,7 @@
         <v>782</v>
       </c>
     </row>
-    <row r="344" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="344" spans="2:7" ht="18" customHeight="1">
       <c r="B344" t="s">
         <v>783</v>
       </c>
@@ -11993,7 +11991,7 @@
         <v>785</v>
       </c>
     </row>
-    <row r="345" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="345" spans="2:7" ht="18" customHeight="1">
       <c r="B345" t="s">
         <v>448</v>
       </c>
@@ -12013,7 +12011,7 @@
         <v>787</v>
       </c>
     </row>
-    <row r="346" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="346" spans="2:7" ht="18" customHeight="1">
       <c r="B346" t="s">
         <v>585</v>
       </c>
@@ -12033,7 +12031,7 @@
         <v>789</v>
       </c>
     </row>
-    <row r="347" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="347" spans="2:7" ht="18" customHeight="1">
       <c r="B347" t="s">
         <v>300</v>
       </c>
@@ -12053,7 +12051,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="348" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="348" spans="2:7" ht="18" customHeight="1">
       <c r="B348" t="s">
         <v>277</v>
       </c>
@@ -12073,7 +12071,7 @@
         <v>792</v>
       </c>
     </row>
-    <row r="349" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="349" spans="2:7" ht="18" customHeight="1">
       <c r="B349" t="s">
         <v>78</v>
       </c>
@@ -12093,7 +12091,7 @@
         <v>771</v>
       </c>
     </row>
-    <row r="350" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="350" spans="2:7" ht="18" customHeight="1">
       <c r="B350" t="s">
         <v>277</v>
       </c>
@@ -12113,7 +12111,7 @@
         <v>795</v>
       </c>
     </row>
-    <row r="351" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="351" spans="2:7" ht="18" customHeight="1">
       <c r="B351" t="s">
         <v>120</v>
       </c>
@@ -12133,7 +12131,7 @@
         <v>797</v>
       </c>
     </row>
-    <row r="352" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="352" spans="2:7" ht="18" customHeight="1">
       <c r="B352" t="s">
         <v>129</v>
       </c>
@@ -12153,7 +12151,7 @@
         <v>799</v>
       </c>
     </row>
-    <row r="353" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="353" spans="2:7" ht="18" customHeight="1">
       <c r="B353" t="s">
         <v>800</v>
       </c>
@@ -12173,7 +12171,7 @@
         <v>802</v>
       </c>
     </row>
-    <row r="354" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="354" spans="2:7" ht="18" customHeight="1">
       <c r="B354" t="s">
         <v>441</v>
       </c>
@@ -12193,7 +12191,7 @@
         <v>804</v>
       </c>
     </row>
-    <row r="355" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="355" spans="2:7" ht="18" customHeight="1">
       <c r="B355" t="s">
         <v>249</v>
       </c>
@@ -12213,7 +12211,7 @@
         <v>806</v>
       </c>
     </row>
-    <row r="356" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="356" spans="2:7" ht="18" customHeight="1">
       <c r="B356" t="s">
         <v>432</v>
       </c>
@@ -12233,7 +12231,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="357" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="357" spans="2:7" ht="18" customHeight="1">
       <c r="B357" t="s">
         <v>240</v>
       </c>
@@ -12253,7 +12251,7 @@
         <v>809</v>
       </c>
     </row>
-    <row r="358" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="358" spans="2:7" ht="18" customHeight="1">
       <c r="B358" t="s">
         <v>135</v>
       </c>
@@ -12273,7 +12271,7 @@
         <v>811</v>
       </c>
     </row>
-    <row r="359" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="359" spans="2:7" ht="18" customHeight="1">
       <c r="B359" t="s">
         <v>190</v>
       </c>
@@ -12293,7 +12291,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="360" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="360" spans="2:7" ht="18" customHeight="1">
       <c r="B360" t="s">
         <v>814</v>
       </c>
@@ -12313,7 +12311,7 @@
         <v>816</v>
       </c>
     </row>
-    <row r="361" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="361" spans="2:7" ht="18" customHeight="1">
       <c r="B361" t="s">
         <v>105</v>
       </c>
@@ -12333,7 +12331,7 @@
         <v>732</v>
       </c>
     </row>
-    <row r="362" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="362" spans="2:7" ht="18" customHeight="1">
       <c r="B362" t="s">
         <v>78</v>
       </c>
@@ -12353,7 +12351,7 @@
         <v>819</v>
       </c>
     </row>
-    <row r="363" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="363" spans="2:7" ht="18" customHeight="1">
       <c r="B363" t="s">
         <v>820</v>
       </c>
@@ -12373,7 +12371,7 @@
         <v>822</v>
       </c>
     </row>
-    <row r="364" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="364" spans="2:7" ht="18" customHeight="1">
       <c r="B364" t="s">
         <v>741</v>
       </c>
@@ -12393,7 +12391,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="365" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="365" spans="2:7" ht="18" customHeight="1">
       <c r="B365" t="s">
         <v>825</v>
       </c>
@@ -12413,7 +12411,7 @@
         <v>827</v>
       </c>
     </row>
-    <row r="366" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="366" spans="2:7" ht="18" customHeight="1">
       <c r="B366" t="s">
         <v>274</v>
       </c>
@@ -12433,7 +12431,7 @@
         <v>738</v>
       </c>
     </row>
-    <row r="367" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="367" spans="2:7" ht="18" customHeight="1">
       <c r="B367" t="s">
         <v>132</v>
       </c>
@@ -12453,7 +12451,7 @@
         <v>830</v>
       </c>
     </row>
-    <row r="368" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="368" spans="2:7" ht="18" customHeight="1">
       <c r="B368" t="s">
         <v>96</v>
       </c>
@@ -12473,7 +12471,7 @@
         <v>782</v>
       </c>
     </row>
-    <row r="369" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="369" spans="2:7" ht="18" customHeight="1">
       <c r="B369" t="s">
         <v>415</v>
       </c>
@@ -12493,7 +12491,7 @@
         <v>833</v>
       </c>
     </row>
-    <row r="370" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="370" spans="2:7" ht="18" customHeight="1">
       <c r="B370" t="s">
         <v>108</v>
       </c>
@@ -12513,7 +12511,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="371" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="371" spans="2:7" ht="18" customHeight="1">
       <c r="B371" t="s">
         <v>300</v>
       </c>
@@ -12533,7 +12531,7 @@
         <v>837</v>
       </c>
     </row>
-    <row r="372" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="372" spans="2:7" ht="18" customHeight="1">
       <c r="B372" t="s">
         <v>277</v>
       </c>
@@ -12553,7 +12551,7 @@
         <v>839</v>
       </c>
     </row>
-    <row r="373" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="373" spans="2:7" ht="18" customHeight="1">
       <c r="B373" t="s">
         <v>240</v>
       </c>
@@ -12573,7 +12571,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="374" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="374" spans="2:7" ht="18" customHeight="1">
       <c r="B374" t="s">
         <v>841</v>
       </c>
@@ -12593,7 +12591,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="375" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="375" spans="2:7" ht="18" customHeight="1">
       <c r="B375" t="s">
         <v>78</v>
       </c>
@@ -12613,7 +12611,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="376" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="376" spans="2:7" ht="18" customHeight="1">
       <c r="B376" t="s">
         <v>117</v>
       </c>
@@ -12633,7 +12631,7 @@
         <v>847</v>
       </c>
     </row>
-    <row r="377" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="377" spans="2:7" ht="18" customHeight="1">
       <c r="B377" t="s">
         <v>105</v>
       </c>
@@ -12653,7 +12651,7 @@
         <v>849</v>
       </c>
     </row>
-    <row r="378" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="378" spans="2:7" ht="18" customHeight="1">
       <c r="B378" t="s">
         <v>112</v>
       </c>
@@ -12673,7 +12671,7 @@
         <v>851</v>
       </c>
     </row>
-    <row r="379" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="379" spans="2:7" ht="18" customHeight="1">
       <c r="B379" t="s">
         <v>135</v>
       </c>
@@ -12693,7 +12691,7 @@
         <v>811</v>
       </c>
     </row>
-    <row r="380" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="380" spans="2:7" ht="18" customHeight="1">
       <c r="B380" t="s">
         <v>112</v>
       </c>
@@ -12713,7 +12711,7 @@
         <v>854</v>
       </c>
     </row>
-    <row r="381" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="381" spans="2:7" ht="18" customHeight="1">
       <c r="B381" t="s">
         <v>505</v>
       </c>
@@ -12733,7 +12731,7 @@
         <v>856</v>
       </c>
     </row>
-    <row r="382" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="382" spans="2:7" ht="18" customHeight="1">
       <c r="B382" t="s">
         <v>204</v>
       </c>
@@ -12753,7 +12751,7 @@
         <v>858</v>
       </c>
     </row>
-    <row r="383" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="383" spans="2:7" ht="18" customHeight="1">
       <c r="B383" t="s">
         <v>369</v>
       </c>
@@ -12773,7 +12771,7 @@
         <v>860</v>
       </c>
     </row>
-    <row r="384" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="384" spans="2:7" ht="18" customHeight="1">
       <c r="B384" t="s">
         <v>144</v>
       </c>
@@ -12793,7 +12791,7 @@
         <v>862</v>
       </c>
     </row>
-    <row r="385" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="385" spans="2:7" ht="18" customHeight="1">
       <c r="B385" t="s">
         <v>313</v>
       </c>
@@ -12813,7 +12811,7 @@
         <v>864</v>
       </c>
     </row>
-    <row r="386" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="386" spans="2:7" ht="18" customHeight="1">
       <c r="B386" t="s">
         <v>163</v>
       </c>
@@ -12833,7 +12831,7 @@
         <v>730</v>
       </c>
     </row>
-    <row r="387" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="387" spans="2:7" ht="18" customHeight="1">
       <c r="B387" t="s">
         <v>163</v>
       </c>
@@ -12853,7 +12851,7 @@
         <v>730</v>
       </c>
     </row>
-    <row r="388" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="388" spans="2:7" ht="18" customHeight="1">
       <c r="B388" t="s">
         <v>320</v>
       </c>
@@ -12873,7 +12871,7 @@
         <v>868</v>
       </c>
     </row>
-    <row r="389" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="389" spans="2:7" ht="18" customHeight="1">
       <c r="B389" t="s">
         <v>262</v>
       </c>
@@ -12893,7 +12891,7 @@
         <v>870</v>
       </c>
     </row>
-    <row r="390" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="390" spans="2:7" ht="18" customHeight="1">
       <c r="B390" t="s">
         <v>135</v>
       </c>
@@ -12913,7 +12911,7 @@
         <v>872</v>
       </c>
     </row>
-    <row r="391" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="391" spans="2:7" ht="18" customHeight="1">
       <c r="B391" t="s">
         <v>401</v>
       </c>
@@ -12933,7 +12931,7 @@
         <v>874</v>
       </c>
     </row>
-    <row r="392" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="392" spans="2:7" ht="18" customHeight="1">
       <c r="B392" t="s">
         <v>741</v>
       </c>
@@ -12953,7 +12951,7 @@
         <v>876</v>
       </c>
     </row>
-    <row r="393" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="393" spans="2:7" ht="18" customHeight="1">
       <c r="B393" t="s">
         <v>135</v>
       </c>
@@ -12973,7 +12971,7 @@
         <v>878</v>
       </c>
     </row>
-    <row r="394" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="394" spans="2:7" ht="18" customHeight="1">
       <c r="B394" t="s">
         <v>879</v>
       </c>
@@ -12993,7 +12991,7 @@
         <v>881</v>
       </c>
     </row>
-    <row r="395" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="395" spans="2:7" ht="18" customHeight="1">
       <c r="B395" t="s">
         <v>132</v>
       </c>
@@ -13013,7 +13011,7 @@
         <v>883</v>
       </c>
     </row>
-    <row r="396" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="396" spans="2:7" ht="18" customHeight="1">
       <c r="B396" t="s">
         <v>151</v>
       </c>
@@ -13033,7 +13031,7 @@
         <v>883</v>
       </c>
     </row>
-    <row r="397" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="397" spans="2:7" ht="18" customHeight="1">
       <c r="B397" t="s">
         <v>105</v>
       </c>
@@ -13053,7 +13051,7 @@
         <v>885</v>
       </c>
     </row>
-    <row r="398" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="398" spans="2:7" ht="18" customHeight="1">
       <c r="B398" t="s">
         <v>432</v>
       </c>
@@ -13073,7 +13071,7 @@
         <v>887</v>
       </c>
     </row>
-    <row r="399" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="399" spans="2:7" ht="18" customHeight="1">
       <c r="B399" t="s">
         <v>274</v>
       </c>
@@ -13093,7 +13091,7 @@
         <v>889</v>
       </c>
     </row>
-    <row r="400" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="400" spans="2:7" ht="18" customHeight="1">
       <c r="B400" t="s">
         <v>710</v>
       </c>
@@ -13113,7 +13111,7 @@
         <v>891</v>
       </c>
     </row>
-    <row r="401" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="401" spans="2:7" ht="18" customHeight="1">
       <c r="B401" t="s">
         <v>415</v>
       </c>
@@ -13133,7 +13131,7 @@
         <v>893</v>
       </c>
     </row>
-    <row r="402" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="402" spans="2:7" ht="18" customHeight="1">
       <c r="B402" t="s">
         <v>151</v>
       </c>
@@ -13153,7 +13151,7 @@
         <v>895</v>
       </c>
     </row>
-    <row r="403" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="403" spans="2:7" ht="18" customHeight="1">
       <c r="B403" t="s">
         <v>42</v>
       </c>
@@ -13173,7 +13171,7 @@
         <v>897</v>
       </c>
     </row>
-    <row r="404" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="404" spans="2:7" ht="18" customHeight="1">
       <c r="B404" t="s">
         <v>166</v>
       </c>
@@ -13193,7 +13191,7 @@
         <v>724</v>
       </c>
     </row>
-    <row r="405" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="405" spans="2:7" ht="18" customHeight="1">
       <c r="B405" t="s">
         <v>210</v>
       </c>
@@ -13213,7 +13211,7 @@
         <v>899</v>
       </c>
     </row>
-    <row r="406" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="406" spans="2:7" ht="18" customHeight="1">
       <c r="B406" t="s">
         <v>274</v>
       </c>
@@ -13233,7 +13231,7 @@
         <v>738</v>
       </c>
     </row>
-    <row r="407" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="407" spans="2:7" ht="18" customHeight="1">
       <c r="B407" t="s">
         <v>207</v>
       </c>
@@ -13253,7 +13251,7 @@
         <v>902</v>
       </c>
     </row>
-    <row r="408" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="408" spans="2:7" ht="18" customHeight="1">
       <c r="B408" t="s">
         <v>510</v>
       </c>
@@ -13273,7 +13271,7 @@
         <v>904</v>
       </c>
     </row>
-    <row r="409" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="409" spans="2:7" ht="18" customHeight="1">
       <c r="B409" t="s">
         <v>262</v>
       </c>
@@ -13293,7 +13291,7 @@
         <v>906</v>
       </c>
     </row>
-    <row r="410" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="410" spans="2:7" ht="18" customHeight="1">
       <c r="B410" t="s">
         <v>190</v>
       </c>
@@ -13313,7 +13311,7 @@
         <v>908</v>
       </c>
     </row>
-    <row r="411" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="411" spans="2:7" ht="18" customHeight="1">
       <c r="B411" t="s">
         <v>171</v>
       </c>
@@ -13333,7 +13331,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="412" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="412" spans="2:7" ht="18" customHeight="1">
       <c r="B412" t="s">
         <v>341</v>
       </c>
@@ -13353,7 +13351,7 @@
         <v>911</v>
       </c>
     </row>
-    <row r="413" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="413" spans="2:7" ht="18" customHeight="1">
       <c r="B413" t="s">
         <v>151</v>
       </c>
@@ -13373,7 +13371,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="414" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="414" spans="2:7" ht="18" customHeight="1">
       <c r="B414" t="s">
         <v>252</v>
       </c>
@@ -13393,7 +13391,7 @@
         <v>914</v>
       </c>
     </row>
-    <row r="415" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="415" spans="2:7" ht="18" customHeight="1">
       <c r="B415" t="s">
         <v>415</v>
       </c>
@@ -13413,7 +13411,7 @@
         <v>916</v>
       </c>
     </row>
-    <row r="416" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="416" spans="2:7" ht="18" customHeight="1">
       <c r="B416" t="s">
         <v>240</v>
       </c>
@@ -13433,7 +13431,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="417" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="417" spans="2:7" ht="18" customHeight="1">
       <c r="B417" t="s">
         <v>505</v>
       </c>
@@ -13453,7 +13451,7 @@
         <v>918</v>
       </c>
     </row>
-    <row r="418" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="418" spans="2:7" ht="18" customHeight="1">
       <c r="B418" t="s">
         <v>841</v>
       </c>
@@ -13473,7 +13471,7 @@
         <v>920</v>
       </c>
     </row>
-    <row r="419" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="419" spans="2:7" ht="18" customHeight="1">
       <c r="B419" t="s">
         <v>132</v>
       </c>
@@ -13493,7 +13491,7 @@
         <v>922</v>
       </c>
     </row>
-    <row r="420" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="420" spans="2:7" ht="18" customHeight="1">
       <c r="B420" t="s">
         <v>132</v>
       </c>
@@ -13513,7 +13511,7 @@
         <v>924</v>
       </c>
     </row>
-    <row r="421" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="421" spans="2:7" ht="18" customHeight="1">
       <c r="B421" t="s">
         <v>132</v>
       </c>
@@ -13533,7 +13531,7 @@
         <v>926</v>
       </c>
     </row>
-    <row r="422" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="422" spans="2:7" ht="18" customHeight="1">
       <c r="B422" t="s">
         <v>297</v>
       </c>
@@ -13553,7 +13551,7 @@
         <v>928</v>
       </c>
     </row>
-    <row r="423" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="423" spans="2:7" ht="18" customHeight="1">
       <c r="B423" t="s">
         <v>249</v>
       </c>
@@ -13573,7 +13571,7 @@
         <v>930</v>
       </c>
     </row>
-    <row r="424" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="424" spans="2:7" ht="18" customHeight="1">
       <c r="B424" t="s">
         <v>666</v>
       </c>
@@ -13593,7 +13591,7 @@
         <v>932</v>
       </c>
     </row>
-    <row r="425" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="425" spans="2:7" ht="18" customHeight="1">
       <c r="B425" t="s">
         <v>933</v>
       </c>
@@ -13613,7 +13611,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="426" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="426" spans="2:7" ht="18" customHeight="1">
       <c r="B426" t="s">
         <v>415</v>
       </c>
@@ -13633,7 +13631,7 @@
         <v>937</v>
       </c>
     </row>
-    <row r="427" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="427" spans="2:7" ht="18" customHeight="1">
       <c r="B427" t="s">
         <v>171</v>
       </c>
@@ -13653,7 +13651,7 @@
         <v>688</v>
       </c>
     </row>
-    <row r="428" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="428" spans="2:7" ht="18" customHeight="1">
       <c r="B428" t="s">
         <v>151</v>
       </c>
@@ -13673,7 +13671,7 @@
         <v>940</v>
       </c>
     </row>
-    <row r="429" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="429" spans="2:7" ht="18" customHeight="1">
       <c r="B429" t="s">
         <v>135</v>
       </c>
@@ -13693,7 +13691,7 @@
         <v>942</v>
       </c>
     </row>
-    <row r="430" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="430" spans="2:7" ht="18" customHeight="1">
       <c r="B430" t="s">
         <v>117</v>
       </c>
@@ -13713,7 +13711,7 @@
         <v>944</v>
       </c>
     </row>
-    <row r="431" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="431" spans="2:7" ht="18" customHeight="1">
       <c r="B431" t="s">
         <v>151</v>
       </c>
@@ -13733,7 +13731,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="432" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="432" spans="2:7" ht="18" customHeight="1">
       <c r="B432" t="s">
         <v>946</v>
       </c>
@@ -13753,7 +13751,7 @@
         <v>948</v>
       </c>
     </row>
-    <row r="433" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="433" spans="1:7" ht="18" customHeight="1">
       <c r="B433" t="s">
         <v>135</v>
       </c>
@@ -13773,7 +13771,7 @@
         <v>950</v>
       </c>
     </row>
-    <row r="434" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="434" spans="1:7" ht="18" customHeight="1">
       <c r="B434" t="s">
         <v>510</v>
       </c>
@@ -13793,7 +13791,7 @@
         <v>952</v>
       </c>
     </row>
-    <row r="435" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="435" spans="1:7" ht="18" customHeight="1">
       <c r="B435" t="s">
         <v>953</v>
       </c>
@@ -13813,7 +13811,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="436" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="436" spans="1:7" ht="18" customHeight="1">
       <c r="B436" t="s">
         <v>277</v>
       </c>
@@ -13833,7 +13831,7 @@
         <v>957</v>
       </c>
     </row>
-    <row r="437" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="437" spans="1:7" ht="18" customHeight="1">
       <c r="B437" t="s">
         <v>257</v>
       </c>
@@ -13853,7 +13851,7 @@
         <v>960</v>
       </c>
     </row>
-    <row r="438" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="438" spans="1:7" ht="18" customHeight="1">
       <c r="B438" t="s">
         <v>96</v>
       </c>
@@ -13873,7 +13871,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="439" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="439" spans="1:7" ht="18" customHeight="1">
       <c r="A439" t="s">
         <v>962</v>
       </c>
@@ -13896,7 +13894,7 @@
         <v>964</v>
       </c>
     </row>
-    <row r="440" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="440" spans="1:7" ht="18" customHeight="1">
       <c r="A440" t="s">
         <v>962</v>
       </c>
@@ -13919,7 +13917,7 @@
         <v>966</v>
       </c>
     </row>
-    <row r="441" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="441" spans="1:7" ht="18" customHeight="1">
       <c r="A441" t="s">
         <v>967</v>
       </c>
@@ -13940,7 +13938,7 @@
         <v>969</v>
       </c>
     </row>
-    <row r="442" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="442" spans="1:7" ht="18" customHeight="1">
       <c r="A442" t="s">
         <v>967</v>
       </c>
@@ -13961,7 +13959,7 @@
         <v>971</v>
       </c>
     </row>
-    <row r="443" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="443" spans="1:7" ht="18" customHeight="1">
       <c r="A443" t="s">
         <v>967</v>
       </c>
@@ -13982,7 +13980,7 @@
         <v>973</v>
       </c>
     </row>
-    <row r="444" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="444" spans="1:7" ht="18" customHeight="1">
       <c r="A444" t="s">
         <v>967</v>
       </c>
@@ -14005,7 +14003,7 @@
         <v>975</v>
       </c>
     </row>
-    <row r="445" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="445" spans="1:7">
       <c r="A445" t="s">
         <v>967</v>
       </c>
@@ -14022,13 +14020,13 @@
         <v>45673</v>
       </c>
       <c r="F445" t="s">
+        <v>976</v>
+      </c>
+      <c r="G445" t="s">
         <v>977</v>
       </c>
-      <c r="G445" t="s">
-        <v>978</v>
-      </c>
-    </row>
-    <row r="446" spans="1:7" x14ac:dyDescent="0.2">
+    </row>
+    <row r="446" spans="1:7">
       <c r="A446" t="s">
         <v>962</v>
       </c>
@@ -14045,30 +14043,30 @@
         <v>45673</v>
       </c>
       <c r="F446" t="s">
+        <v>978</v>
+      </c>
+      <c r="G446" t="s">
         <v>979</v>
       </c>
-      <c r="G446" t="s">
-        <v>980</v>
-      </c>
-    </row>
-    <row r="447" spans="1:7" x14ac:dyDescent="0.2">
+    </row>
+    <row r="447" spans="1:7">
       <c r="A447" t="s">
         <v>962</v>
       </c>
       <c r="B447" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="E447" s="12">
         <v>45680</v>
       </c>
       <c r="F447" t="s">
-        <v>1100</v>
+        <v>981</v>
       </c>
       <c r="G447" t="s">
-        <v>1101</v>
-      </c>
-    </row>
-    <row r="448" spans="1:7" x14ac:dyDescent="0.2">
+        <v>982</v>
+      </c>
+    </row>
+    <row r="448" spans="1:7">
       <c r="A448" t="s">
         <v>967</v>
       </c>
@@ -14085,15 +14083,15 @@
         <v>45682</v>
       </c>
       <c r="F448" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="G448" t="s">
-        <v>983</v>
-      </c>
-    </row>
-    <row r="449" spans="1:7" x14ac:dyDescent="0.2">
+        <v>984</v>
+      </c>
+    </row>
+    <row r="449" spans="1:7">
       <c r="A449" t="s">
-        <v>976</v>
+        <v>985</v>
       </c>
       <c r="B449" t="s">
         <v>435</v>
@@ -14108,13 +14106,13 @@
         <v>45685</v>
       </c>
       <c r="F449" t="s">
-        <v>984</v>
+        <v>986</v>
       </c>
       <c r="G449" t="s">
-        <v>985</v>
-      </c>
-    </row>
-    <row r="450" spans="1:7" x14ac:dyDescent="0.2">
+        <v>987</v>
+      </c>
+    </row>
+    <row r="450" spans="1:7">
       <c r="B450" t="s">
         <v>58</v>
       </c>
@@ -14128,13 +14126,13 @@
         <v>45689</v>
       </c>
       <c r="F450" t="s">
-        <v>986</v>
+        <v>988</v>
       </c>
       <c r="G450" t="s">
-        <v>987</v>
-      </c>
-    </row>
-    <row r="451" spans="1:7" x14ac:dyDescent="0.2">
+        <v>989</v>
+      </c>
+    </row>
+    <row r="451" spans="1:7">
       <c r="B451" t="s">
         <v>313</v>
       </c>
@@ -14148,13 +14146,13 @@
         <v>45689</v>
       </c>
       <c r="F451" t="s">
-        <v>988</v>
+        <v>990</v>
       </c>
       <c r="G451" t="s">
-        <v>989</v>
-      </c>
-    </row>
-    <row r="452" spans="1:7" x14ac:dyDescent="0.2">
+        <v>991</v>
+      </c>
+    </row>
+    <row r="452" spans="1:7">
       <c r="B452" t="s">
         <v>510</v>
       </c>
@@ -14168,13 +14166,13 @@
         <v>45691</v>
       </c>
       <c r="F452" t="s">
-        <v>990</v>
+        <v>992</v>
       </c>
       <c r="G452" t="s">
-        <v>991</v>
-      </c>
-    </row>
-    <row r="453" spans="1:7" x14ac:dyDescent="0.2">
+        <v>993</v>
+      </c>
+    </row>
+    <row r="453" spans="1:7">
       <c r="B453" t="s">
         <v>585</v>
       </c>
@@ -14188,13 +14186,13 @@
         <v>45692</v>
       </c>
       <c r="F453" t="s">
-        <v>992</v>
+        <v>994</v>
       </c>
       <c r="G453" t="s">
-        <v>993</v>
-      </c>
-    </row>
-    <row r="454" spans="1:7" x14ac:dyDescent="0.2">
+        <v>995</v>
+      </c>
+    </row>
+    <row r="454" spans="1:7">
       <c r="B454" t="s">
         <v>135</v>
       </c>
@@ -14208,13 +14206,13 @@
         <v>45692</v>
       </c>
       <c r="F454" t="s">
-        <v>994</v>
+        <v>996</v>
       </c>
       <c r="G454" t="s">
-        <v>995</v>
-      </c>
-    </row>
-    <row r="455" spans="1:7" x14ac:dyDescent="0.2">
+        <v>997</v>
+      </c>
+    </row>
+    <row r="455" spans="1:7">
       <c r="B455" t="s">
         <v>666</v>
       </c>
@@ -14228,13 +14226,13 @@
         <v>45693</v>
       </c>
       <c r="F455" t="s">
-        <v>996</v>
+        <v>998</v>
       </c>
       <c r="G455" t="s">
-        <v>997</v>
-      </c>
-    </row>
-    <row r="456" spans="1:7" x14ac:dyDescent="0.2">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="456" spans="1:7">
       <c r="B456" t="s">
         <v>666</v>
       </c>
@@ -14248,13 +14246,13 @@
         <v>45693</v>
       </c>
       <c r="F456" t="s">
-        <v>998</v>
+        <v>1000</v>
       </c>
       <c r="G456" t="s">
-        <v>999</v>
-      </c>
-    </row>
-    <row r="457" spans="1:7" x14ac:dyDescent="0.2">
+        <v>1001</v>
+      </c>
+    </row>
+    <row r="457" spans="1:7">
       <c r="B457" t="s">
         <v>415</v>
       </c>
@@ -14268,13 +14266,13 @@
         <v>45693</v>
       </c>
       <c r="F457" t="s">
-        <v>1000</v>
+        <v>1002</v>
       </c>
       <c r="G457" t="s">
-        <v>1001</v>
-      </c>
-    </row>
-    <row r="458" spans="1:7" x14ac:dyDescent="0.2">
+        <v>1003</v>
+      </c>
+    </row>
+    <row r="458" spans="1:7">
       <c r="B458" t="s">
         <v>96</v>
       </c>
@@ -14288,13 +14286,13 @@
         <v>45693</v>
       </c>
       <c r="F458" t="s">
-        <v>1002</v>
+        <v>1004</v>
       </c>
       <c r="G458" t="s">
-        <v>1003</v>
-      </c>
-    </row>
-    <row r="459" spans="1:7" x14ac:dyDescent="0.2">
+        <v>1005</v>
+      </c>
+    </row>
+    <row r="459" spans="1:7">
       <c r="B459" t="s">
         <v>78</v>
       </c>
@@ -14308,13 +14306,13 @@
         <v>45693</v>
       </c>
       <c r="F459" t="s">
-        <v>1004</v>
+        <v>1006</v>
       </c>
       <c r="G459" t="s">
-        <v>1005</v>
-      </c>
-    </row>
-    <row r="460" spans="1:7" x14ac:dyDescent="0.2">
+        <v>1007</v>
+      </c>
+    </row>
+    <row r="460" spans="1:7">
       <c r="B460" t="s">
         <v>163</v>
       </c>
@@ -14328,13 +14326,13 @@
         <v>45693</v>
       </c>
       <c r="F460" t="s">
-        <v>1006</v>
+        <v>1008</v>
       </c>
       <c r="G460" t="s">
-        <v>1007</v>
-      </c>
-    </row>
-    <row r="461" spans="1:7" x14ac:dyDescent="0.2">
+        <v>1009</v>
+      </c>
+    </row>
+    <row r="461" spans="1:7">
       <c r="B461" t="s">
         <v>320</v>
       </c>
@@ -14348,15 +14346,15 @@
         <v>45693</v>
       </c>
       <c r="F461" t="s">
-        <v>1008</v>
+        <v>1010</v>
       </c>
       <c r="G461" t="s">
         <v>868</v>
       </c>
     </row>
-    <row r="462" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="462" spans="1:7">
       <c r="B462" t="s">
-        <v>1009</v>
+        <v>1011</v>
       </c>
       <c r="C462" s="11">
         <v>233657</v>
@@ -14368,13 +14366,13 @@
         <v>45698</v>
       </c>
       <c r="F462" t="s">
-        <v>1010</v>
+        <v>1012</v>
       </c>
       <c r="G462" t="s">
-        <v>1011</v>
-      </c>
-    </row>
-    <row r="463" spans="1:7" x14ac:dyDescent="0.2">
+        <v>1013</v>
+      </c>
+    </row>
+    <row r="463" spans="1:7">
       <c r="B463" t="s">
         <v>297</v>
       </c>
@@ -14388,13 +14386,13 @@
         <v>45706</v>
       </c>
       <c r="F463" t="s">
-        <v>1012</v>
+        <v>1014</v>
       </c>
       <c r="G463" t="s">
-        <v>1013</v>
-      </c>
-    </row>
-    <row r="464" spans="1:7" x14ac:dyDescent="0.2">
+        <v>1015</v>
+      </c>
+    </row>
+    <row r="464" spans="1:7">
       <c r="B464" t="s">
         <v>96</v>
       </c>
@@ -14408,13 +14406,13 @@
         <v>45706</v>
       </c>
       <c r="F464" t="s">
-        <v>1014</v>
+        <v>1016</v>
       </c>
       <c r="G464" t="s">
-        <v>1015</v>
-      </c>
-    </row>
-    <row r="465" spans="2:7" x14ac:dyDescent="0.2">
+        <v>1017</v>
+      </c>
+    </row>
+    <row r="465" spans="2:7">
       <c r="B465" t="s">
         <v>179</v>
       </c>
@@ -14428,13 +14426,13 @@
         <v>45706</v>
       </c>
       <c r="F465" t="s">
-        <v>1016</v>
+        <v>1018</v>
       </c>
       <c r="G465" t="s">
-        <v>1017</v>
-      </c>
-    </row>
-    <row r="466" spans="2:7" x14ac:dyDescent="0.2">
+        <v>1019</v>
+      </c>
+    </row>
+    <row r="466" spans="2:7">
       <c r="B466" t="s">
         <v>415</v>
       </c>
@@ -14448,13 +14446,13 @@
         <v>45706</v>
       </c>
       <c r="F466" t="s">
-        <v>1018</v>
+        <v>1020</v>
       </c>
       <c r="G466" t="s">
-        <v>1019</v>
-      </c>
-    </row>
-    <row r="467" spans="2:7" x14ac:dyDescent="0.2">
+        <v>1021</v>
+      </c>
+    </row>
+    <row r="467" spans="2:7">
       <c r="B467" t="s">
         <v>252</v>
       </c>
@@ -14468,15 +14466,15 @@
         <v>45706</v>
       </c>
       <c r="F467" t="s">
-        <v>1020</v>
+        <v>1022</v>
       </c>
       <c r="G467" t="s">
-        <v>1021</v>
-      </c>
-    </row>
-    <row r="468" spans="2:7" x14ac:dyDescent="0.2">
+        <v>1023</v>
+      </c>
+    </row>
+    <row r="468" spans="2:7">
       <c r="B468" t="s">
-        <v>1022</v>
+        <v>1024</v>
       </c>
       <c r="C468" s="11">
         <v>233639</v>
@@ -14488,13 +14486,13 @@
         <v>45706</v>
       </c>
       <c r="F468" t="s">
-        <v>1023</v>
+        <v>1025</v>
       </c>
       <c r="G468" t="s">
-        <v>1024</v>
-      </c>
-    </row>
-    <row r="469" spans="2:7" x14ac:dyDescent="0.2">
+        <v>1026</v>
+      </c>
+    </row>
+    <row r="469" spans="2:7">
       <c r="B469" t="s">
         <v>84</v>
       </c>
@@ -14508,13 +14506,13 @@
         <v>45707</v>
       </c>
       <c r="F469" t="s">
-        <v>1025</v>
+        <v>1027</v>
       </c>
       <c r="G469" t="s">
-        <v>1026</v>
-      </c>
-    </row>
-    <row r="470" spans="2:7" x14ac:dyDescent="0.2">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="470" spans="2:7">
       <c r="B470" t="s">
         <v>78</v>
       </c>
@@ -14528,13 +14526,13 @@
         <v>45712</v>
       </c>
       <c r="F470" t="s">
-        <v>1027</v>
+        <v>1029</v>
       </c>
       <c r="G470" t="s">
-        <v>1028</v>
-      </c>
-    </row>
-    <row r="471" spans="2:7" x14ac:dyDescent="0.2">
+        <v>1030</v>
+      </c>
+    </row>
+    <row r="471" spans="2:7">
       <c r="B471" t="s">
         <v>313</v>
       </c>
@@ -14548,13 +14546,13 @@
         <v>45717</v>
       </c>
       <c r="F471" t="s">
-        <v>1029</v>
+        <v>1031</v>
       </c>
       <c r="G471" t="s">
-        <v>1030</v>
-      </c>
-    </row>
-    <row r="472" spans="2:7" x14ac:dyDescent="0.2">
+        <v>1032</v>
+      </c>
+    </row>
+    <row r="472" spans="2:7">
       <c r="B472" t="s">
         <v>390</v>
       </c>
@@ -14568,13 +14566,13 @@
         <v>45717</v>
       </c>
       <c r="F472" t="s">
-        <v>1031</v>
+        <v>1033</v>
       </c>
       <c r="G472" t="s">
-        <v>1032</v>
-      </c>
-    </row>
-    <row r="473" spans="2:7" x14ac:dyDescent="0.2">
+        <v>1034</v>
+      </c>
+    </row>
+    <row r="473" spans="2:7">
       <c r="B473" t="s">
         <v>390</v>
       </c>
@@ -14588,13 +14586,13 @@
         <v>45720</v>
       </c>
       <c r="F473" t="s">
-        <v>1033</v>
+        <v>1035</v>
       </c>
       <c r="G473" t="s">
-        <v>1034</v>
-      </c>
-    </row>
-    <row r="474" spans="2:7" x14ac:dyDescent="0.2">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="474" spans="2:7">
       <c r="B474" t="s">
         <v>946</v>
       </c>
@@ -14608,13 +14606,13 @@
         <v>45721</v>
       </c>
       <c r="F474" t="s">
-        <v>1035</v>
+        <v>1037</v>
       </c>
       <c r="G474" t="s">
-        <v>1036</v>
-      </c>
-    </row>
-    <row r="475" spans="2:7" x14ac:dyDescent="0.2">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="475" spans="2:7">
       <c r="B475" t="s">
         <v>252</v>
       </c>
@@ -14628,13 +14626,13 @@
         <v>45721</v>
       </c>
       <c r="F475" t="s">
-        <v>1037</v>
+        <v>1039</v>
       </c>
       <c r="G475" t="s">
-        <v>1038</v>
-      </c>
-    </row>
-    <row r="476" spans="2:7" x14ac:dyDescent="0.2">
+        <v>1040</v>
+      </c>
+    </row>
+    <row r="476" spans="2:7">
       <c r="B476" t="s">
         <v>225</v>
       </c>
@@ -14648,13 +14646,13 @@
         <v>45721</v>
       </c>
       <c r="F476" t="s">
-        <v>1039</v>
+        <v>1041</v>
       </c>
       <c r="G476" t="s">
-        <v>1040</v>
-      </c>
-    </row>
-    <row r="477" spans="2:7" x14ac:dyDescent="0.2">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="477" spans="2:7">
       <c r="B477" t="s">
         <v>132</v>
       </c>
@@ -14668,13 +14666,13 @@
         <v>45721</v>
       </c>
       <c r="F477" t="s">
-        <v>1041</v>
+        <v>1043</v>
       </c>
       <c r="G477" t="s">
-        <v>1042</v>
-      </c>
-    </row>
-    <row r="478" spans="2:7" x14ac:dyDescent="0.2">
+        <v>1044</v>
+      </c>
+    </row>
+    <row r="478" spans="2:7">
       <c r="B478" t="s">
         <v>112</v>
       </c>
@@ -14688,15 +14686,15 @@
         <v>45726</v>
       </c>
       <c r="F478" t="s">
-        <v>1043</v>
+        <v>1045</v>
       </c>
       <c r="G478" t="s">
-        <v>1044</v>
-      </c>
-    </row>
-    <row r="479" spans="2:7" x14ac:dyDescent="0.2">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="479" spans="2:7">
       <c r="B479" t="s">
-        <v>1045</v>
+        <v>1047</v>
       </c>
       <c r="C479" s="11">
         <v>233988</v>
@@ -14708,13 +14706,13 @@
         <v>45727</v>
       </c>
       <c r="F479" t="s">
-        <v>1046</v>
+        <v>1048</v>
       </c>
       <c r="G479" t="s">
-        <v>1047</v>
-      </c>
-    </row>
-    <row r="480" spans="2:7" x14ac:dyDescent="0.2">
+        <v>1049</v>
+      </c>
+    </row>
+    <row r="480" spans="2:7">
       <c r="B480" t="s">
         <v>297</v>
       </c>
@@ -14728,13 +14726,13 @@
         <v>45730</v>
       </c>
       <c r="F480" t="s">
-        <v>1048</v>
+        <v>1050</v>
       </c>
       <c r="G480" t="s">
-        <v>1049</v>
-      </c>
-    </row>
-    <row r="481" spans="1:7" x14ac:dyDescent="0.2">
+        <v>1051</v>
+      </c>
+    </row>
+    <row r="481" spans="1:7">
       <c r="B481" t="s">
         <v>300</v>
       </c>
@@ -14748,13 +14746,13 @@
         <v>45732</v>
       </c>
       <c r="F481" t="s">
-        <v>1050</v>
+        <v>1052</v>
       </c>
       <c r="G481" t="s">
-        <v>1051</v>
-      </c>
-    </row>
-    <row r="482" spans="1:7" x14ac:dyDescent="0.2">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="482" spans="1:7">
       <c r="B482" t="s">
         <v>274</v>
       </c>
@@ -14768,13 +14766,13 @@
         <v>45732</v>
       </c>
       <c r="F482" t="s">
-        <v>1052</v>
+        <v>1054</v>
       </c>
       <c r="G482" t="s">
-        <v>1053</v>
-      </c>
-    </row>
-    <row r="483" spans="1:7" x14ac:dyDescent="0.2">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="483" spans="1:7">
       <c r="B483" t="s">
         <v>61</v>
       </c>
@@ -14788,15 +14786,15 @@
         <v>45733</v>
       </c>
       <c r="F483" t="s">
-        <v>1054</v>
+        <v>1056</v>
       </c>
       <c r="G483" t="s">
-        <v>1055</v>
-      </c>
-    </row>
-    <row r="484" spans="1:7" x14ac:dyDescent="0.2">
+        <v>1057</v>
+      </c>
+    </row>
+    <row r="484" spans="1:7">
       <c r="B484" t="s">
-        <v>1056</v>
+        <v>1058</v>
       </c>
       <c r="C484" s="11">
         <v>234017</v>
@@ -14808,13 +14806,13 @@
         <v>45733</v>
       </c>
       <c r="F484" t="s">
-        <v>1057</v>
+        <v>1059</v>
       </c>
       <c r="G484" t="s">
-        <v>1058</v>
-      </c>
-    </row>
-    <row r="485" spans="1:7" x14ac:dyDescent="0.2">
+        <v>1060</v>
+      </c>
+    </row>
+    <row r="485" spans="1:7">
       <c r="B485" t="s">
         <v>297</v>
       </c>
@@ -14828,13 +14826,13 @@
         <v>45734</v>
       </c>
       <c r="F485" t="s">
-        <v>1059</v>
+        <v>1061</v>
       </c>
       <c r="G485" t="s">
-        <v>1060</v>
-      </c>
-    </row>
-    <row r="486" spans="1:7" x14ac:dyDescent="0.2">
+        <v>1062</v>
+      </c>
+    </row>
+    <row r="486" spans="1:7">
       <c r="B486" t="s">
         <v>297</v>
       </c>
@@ -14848,15 +14846,15 @@
         <v>45741</v>
       </c>
       <c r="F486" t="s">
-        <v>1061</v>
+        <v>1063</v>
       </c>
       <c r="G486" t="s">
-        <v>1062</v>
-      </c>
-    </row>
-    <row r="487" spans="1:7" x14ac:dyDescent="0.2">
+        <v>1064</v>
+      </c>
+    </row>
+    <row r="487" spans="1:7">
       <c r="B487" t="s">
-        <v>1009</v>
+        <v>1011</v>
       </c>
       <c r="C487" s="11">
         <v>234059</v>
@@ -14868,13 +14866,13 @@
         <v>45741</v>
       </c>
       <c r="F487" t="s">
-        <v>1063</v>
+        <v>1065</v>
       </c>
       <c r="G487" t="s">
-        <v>1064</v>
-      </c>
-    </row>
-    <row r="488" spans="1:7" x14ac:dyDescent="0.2">
+        <v>1066</v>
+      </c>
+    </row>
+    <row r="488" spans="1:7">
       <c r="B488" t="s">
         <v>277</v>
       </c>
@@ -14888,15 +14886,15 @@
         <v>45747</v>
       </c>
       <c r="F488" t="s">
-        <v>1065</v>
+        <v>1067</v>
       </c>
       <c r="G488" t="s">
-        <v>1066</v>
-      </c>
-    </row>
-    <row r="489" spans="1:7" x14ac:dyDescent="0.2">
+        <v>1068</v>
+      </c>
+    </row>
+    <row r="489" spans="1:7">
       <c r="B489" t="s">
-        <v>1067</v>
+        <v>1069</v>
       </c>
       <c r="C489" s="11">
         <v>234213</v>
@@ -14908,15 +14906,15 @@
         <v>45747</v>
       </c>
       <c r="F489" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="G489" t="s">
-        <v>1069</v>
-      </c>
-    </row>
-    <row r="490" spans="1:7" x14ac:dyDescent="0.2">
+        <v>1071</v>
+      </c>
+    </row>
+    <row r="490" spans="1:7">
       <c r="B490" t="s">
-        <v>1056</v>
+        <v>1058</v>
       </c>
       <c r="C490" s="11">
         <v>233799</v>
@@ -14928,13 +14926,13 @@
         <v>45747</v>
       </c>
       <c r="F490" t="s">
-        <v>1070</v>
+        <v>1072</v>
       </c>
       <c r="G490" t="s">
-        <v>1071</v>
-      </c>
-    </row>
-    <row r="491" spans="1:7" x14ac:dyDescent="0.2">
+        <v>1073</v>
+      </c>
+    </row>
+    <row r="491" spans="1:7">
       <c r="B491" t="s">
         <v>308</v>
       </c>
@@ -14948,13 +14946,13 @@
         <v>45750</v>
       </c>
       <c r="F491" t="s">
-        <v>1072</v>
+        <v>1074</v>
       </c>
       <c r="G491" t="s">
-        <v>1073</v>
-      </c>
-    </row>
-    <row r="492" spans="1:7" x14ac:dyDescent="0.2">
+        <v>1075</v>
+      </c>
+    </row>
+    <row r="492" spans="1:7">
       <c r="B492" t="s">
         <v>78</v>
       </c>
@@ -14965,15 +14963,15 @@
         <v>45793</v>
       </c>
       <c r="F492" t="s">
-        <v>1074</v>
+        <v>1076</v>
       </c>
       <c r="G492" t="s">
-        <v>1075</v>
-      </c>
-    </row>
-    <row r="493" spans="1:7" x14ac:dyDescent="0.2">
+        <v>1077</v>
+      </c>
+    </row>
+    <row r="493" spans="1:7">
       <c r="A493" t="s">
-        <v>1076</v>
+        <v>1078</v>
       </c>
       <c r="B493" t="s">
         <v>297</v>
@@ -14988,15 +14986,15 @@
         <v>45687</v>
       </c>
       <c r="F493" t="s">
-        <v>1077</v>
+        <v>1079</v>
       </c>
       <c r="G493" t="s">
-        <v>1078</v>
-      </c>
-    </row>
-    <row r="494" spans="1:7" x14ac:dyDescent="0.2">
+        <v>1080</v>
+      </c>
+    </row>
+    <row r="494" spans="1:7">
       <c r="A494" t="s">
-        <v>976</v>
+        <v>985</v>
       </c>
       <c r="B494" t="s">
         <v>46</v>
@@ -15011,18 +15009,18 @@
         <v>45688</v>
       </c>
       <c r="F494" t="s">
-        <v>1079</v>
+        <v>1081</v>
       </c>
       <c r="G494" t="s">
-        <v>1080</v>
-      </c>
-    </row>
-    <row r="495" spans="1:7" x14ac:dyDescent="0.2">
+        <v>1082</v>
+      </c>
+    </row>
+    <row r="495" spans="1:7">
       <c r="A495" t="s">
-        <v>976</v>
+        <v>985</v>
       </c>
       <c r="B495" t="s">
-        <v>1009</v>
+        <v>1011</v>
       </c>
       <c r="C495" s="11">
         <v>233421</v>
@@ -15034,15 +15032,15 @@
         <v>45688</v>
       </c>
       <c r="F495" t="s">
-        <v>1081</v>
+        <v>1083</v>
       </c>
       <c r="G495" t="s">
-        <v>1082</v>
-      </c>
-    </row>
-    <row r="496" spans="1:7" x14ac:dyDescent="0.2">
+        <v>1084</v>
+      </c>
+    </row>
+    <row r="496" spans="1:7">
       <c r="A496" t="s">
-        <v>976</v>
+        <v>985</v>
       </c>
       <c r="B496" t="s">
         <v>390</v>
@@ -15052,9 +15050,9 @@
         <v>45691</v>
       </c>
     </row>
-    <row r="497" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="497" spans="1:5">
       <c r="A497" t="s">
-        <v>1076</v>
+        <v>1078</v>
       </c>
       <c r="B497" t="s">
         <v>320</v>
@@ -15063,7 +15061,7 @@
         <v>45691</v>
       </c>
     </row>
-    <row r="498" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="498" spans="1:5">
       <c r="A498" t="s">
         <v>967</v>
       </c>
@@ -15074,7 +15072,7 @@
         <v>45693</v>
       </c>
     </row>
-    <row r="499" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="499" spans="1:5">
       <c r="A499" t="s">
         <v>962</v>
       </c>
@@ -15085,7 +15083,7 @@
         <v>45693</v>
       </c>
     </row>
-    <row r="500" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="500" spans="1:5">
       <c r="A500" t="s">
         <v>962</v>
       </c>
@@ -15096,7 +15094,7 @@
         <v>45693</v>
       </c>
     </row>
-    <row r="501" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="501" spans="1:5">
       <c r="A501" t="s">
         <v>962</v>
       </c>
@@ -15107,7 +15105,7 @@
         <v>45693</v>
       </c>
     </row>
-    <row r="502" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="502" spans="1:5">
       <c r="A502" t="s">
         <v>962</v>
       </c>
@@ -15118,7 +15116,7 @@
         <v>45702</v>
       </c>
     </row>
-    <row r="503" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="503" spans="1:5">
       <c r="A503" t="s">
         <v>962</v>
       </c>
@@ -15129,9 +15127,9 @@
         <v>45706</v>
       </c>
     </row>
-    <row r="504" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="504" spans="1:5">
       <c r="A504" t="s">
-        <v>976</v>
+        <v>985</v>
       </c>
       <c r="B504" t="s">
         <v>946</v>
@@ -15140,9 +15138,9 @@
         <v>45706</v>
       </c>
     </row>
-    <row r="505" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="505" spans="1:5">
       <c r="A505" t="s">
-        <v>976</v>
+        <v>985</v>
       </c>
       <c r="B505" t="s">
         <v>252</v>
@@ -15151,9 +15149,9 @@
         <v>45707</v>
       </c>
     </row>
-    <row r="506" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="506" spans="1:5">
       <c r="A506" t="s">
-        <v>976</v>
+        <v>985</v>
       </c>
       <c r="B506" t="s">
         <v>344</v>
@@ -15162,9 +15160,9 @@
         <v>45709</v>
       </c>
     </row>
-    <row r="507" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="507" spans="1:5">
       <c r="A507" t="s">
-        <v>976</v>
+        <v>985</v>
       </c>
       <c r="B507" t="s">
         <v>58</v>
@@ -15173,20 +15171,20 @@
         <v>45713</v>
       </c>
     </row>
-    <row r="508" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="508" spans="1:5">
       <c r="A508" t="s">
-        <v>1076</v>
+        <v>1078</v>
       </c>
       <c r="B508" t="s">
-        <v>1056</v>
+        <v>1058</v>
       </c>
       <c r="E508" s="12">
         <v>45715</v>
       </c>
     </row>
-    <row r="509" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="509" spans="1:5">
       <c r="A509" t="s">
-        <v>1076</v>
+        <v>1078</v>
       </c>
       <c r="B509" t="s">
         <v>814</v>
@@ -15195,9 +15193,9 @@
         <v>45716</v>
       </c>
     </row>
-    <row r="510" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="510" spans="1:5">
       <c r="A510" t="s">
-        <v>1076</v>
+        <v>1078</v>
       </c>
       <c r="B510" t="s">
         <v>78</v>
@@ -15206,9 +15204,9 @@
         <v>45716</v>
       </c>
     </row>
-    <row r="511" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="511" spans="1:5">
       <c r="A511" t="s">
-        <v>1076</v>
+        <v>1078</v>
       </c>
       <c r="B511" t="s">
         <v>313</v>
@@ -15217,9 +15215,9 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="512" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="512" spans="1:5">
       <c r="A512" t="s">
-        <v>1076</v>
+        <v>1078</v>
       </c>
       <c r="B512" t="s">
         <v>841</v>
@@ -15228,7 +15226,7 @@
         <v>45719</v>
       </c>
     </row>
-    <row r="513" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="513" spans="1:5">
       <c r="A513" t="s">
         <v>962</v>
       </c>
@@ -15240,7 +15238,7 @@
         <v>45720</v>
       </c>
     </row>
-    <row r="514" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="514" spans="1:5">
       <c r="A514" t="s">
         <v>962</v>
       </c>
@@ -15251,7 +15249,7 @@
         <v>45721</v>
       </c>
     </row>
-    <row r="515" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="515" spans="1:5">
       <c r="A515" t="s">
         <v>962</v>
       </c>
@@ -15262,7 +15260,7 @@
         <v>45721</v>
       </c>
     </row>
-    <row r="516" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="516" spans="1:5">
       <c r="A516" t="s">
         <v>962</v>
       </c>
@@ -15273,7 +15271,7 @@
         <v>45721</v>
       </c>
     </row>
-    <row r="517" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="517" spans="1:5">
       <c r="A517" t="s">
         <v>962</v>
       </c>
@@ -15284,9 +15282,9 @@
         <v>45721</v>
       </c>
     </row>
-    <row r="518" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="518" spans="1:5">
       <c r="A518" t="s">
-        <v>976</v>
+        <v>985</v>
       </c>
       <c r="B518" t="s">
         <v>252</v>
@@ -15295,31 +15293,31 @@
         <v>45721</v>
       </c>
     </row>
-    <row r="519" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="519" spans="1:5">
       <c r="A519" t="s">
-        <v>976</v>
+        <v>985</v>
       </c>
       <c r="B519" t="s">
-        <v>1045</v>
+        <v>1047</v>
       </c>
       <c r="E519" s="12">
         <v>45726</v>
       </c>
     </row>
-    <row r="520" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="520" spans="1:5">
       <c r="A520" t="s">
-        <v>976</v>
+        <v>985</v>
       </c>
       <c r="B520" t="s">
-        <v>1056</v>
+        <v>1058</v>
       </c>
       <c r="E520" s="12">
         <v>45733</v>
       </c>
     </row>
-    <row r="521" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="521" spans="1:5">
       <c r="A521" t="s">
-        <v>1076</v>
+        <v>1078</v>
       </c>
       <c r="B521" t="s">
         <v>300</v>
@@ -15328,9 +15326,9 @@
         <v>45733</v>
       </c>
     </row>
-    <row r="522" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="522" spans="1:5">
       <c r="A522" t="s">
-        <v>1076</v>
+        <v>1078</v>
       </c>
       <c r="B522" t="s">
         <v>61</v>
@@ -15339,9 +15337,9 @@
         <v>45733</v>
       </c>
     </row>
-    <row r="523" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="523" spans="1:5">
       <c r="A523" t="s">
-        <v>1076</v>
+        <v>1078</v>
       </c>
       <c r="B523" t="s">
         <v>274</v>
@@ -15350,7 +15348,7 @@
         <v>45733</v>
       </c>
     </row>
-    <row r="524" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="524" spans="1:5">
       <c r="A524" t="s">
         <v>967</v>
       </c>
@@ -15361,7 +15359,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="525" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="525" spans="1:5">
       <c r="A525" t="s">
         <v>967</v>
       </c>
@@ -15372,7 +15370,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="526" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="526" spans="1:5">
       <c r="A526" t="s">
         <v>967</v>
       </c>
@@ -15383,9 +15381,9 @@
         <v>45750</v>
       </c>
     </row>
-    <row r="527" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="527" spans="1:5">
       <c r="A527" t="s">
-        <v>1076</v>
+        <v>1078</v>
       </c>
       <c r="B527" t="s">
         <v>505</v>
@@ -15394,20 +15392,20 @@
         <v>45763</v>
       </c>
     </row>
-    <row r="528" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="528" spans="1:5">
       <c r="A528" t="s">
-        <v>1076</v>
+        <v>1078</v>
       </c>
       <c r="B528" t="s">
-        <v>1067</v>
+        <v>1069</v>
       </c>
       <c r="E528" s="12">
         <v>45765</v>
       </c>
     </row>
-    <row r="529" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="529" spans="1:5">
       <c r="A529" t="s">
-        <v>1076</v>
+        <v>1078</v>
       </c>
       <c r="B529" t="s">
         <v>252</v>
@@ -15416,18 +15414,18 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="530" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="530" spans="1:5">
       <c r="A530" t="s">
         <v>967</v>
       </c>
       <c r="B530" t="s">
-        <v>1083</v>
+        <v>1085</v>
       </c>
       <c r="E530" s="12">
         <v>45786</v>
       </c>
     </row>
-    <row r="531" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="531" spans="1:5">
       <c r="A531" t="s">
         <v>967</v>
       </c>
@@ -15438,7 +15436,7 @@
         <v>45792</v>
       </c>
     </row>
-    <row r="532" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="532" spans="1:5">
       <c r="A532" t="s">
         <v>967</v>
       </c>
@@ -15449,29 +15447,29 @@
         <v>45793</v>
       </c>
     </row>
-    <row r="533" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="533" spans="1:5">
       <c r="A533" t="s">
         <v>967</v>
       </c>
       <c r="B533" t="s">
-        <v>1102</v>
+        <v>1086</v>
       </c>
       <c r="E533" s="12">
         <v>45793</v>
       </c>
     </row>
-    <row r="534" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="534" spans="1:5">
       <c r="A534" t="s">
-        <v>1084</v>
+        <v>1087</v>
       </c>
       <c r="B534" t="s">
-        <v>1085</v>
+        <v>1088</v>
       </c>
       <c r="E534" s="12">
         <v>45793</v>
       </c>
     </row>
-    <row r="535" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="535" spans="1:5">
       <c r="A535" t="s">
         <v>962</v>
       </c>
@@ -15482,7 +15480,7 @@
         <v>45793</v>
       </c>
     </row>
-    <row r="536" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="536" spans="1:5">
       <c r="A536" t="s">
         <v>962</v>
       </c>
@@ -15493,7 +15491,7 @@
         <v>45793</v>
       </c>
     </row>
-    <row r="537" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="537" spans="1:5">
       <c r="A537" t="s">
         <v>962</v>
       </c>
@@ -15504,7 +15502,7 @@
         <v>45793</v>
       </c>
     </row>
-    <row r="538" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="538" spans="1:5">
       <c r="A538" t="s">
         <v>962</v>
       </c>
@@ -15515,7 +15513,7 @@
         <v>45793</v>
       </c>
     </row>
-    <row r="539" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="539" spans="1:5">
       <c r="A539" t="s">
         <v>962</v>
       </c>
@@ -15526,7 +15524,7 @@
         <v>45793</v>
       </c>
     </row>
-    <row r="540" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="540" spans="1:5">
       <c r="A540" t="s">
         <v>962</v>
       </c>
@@ -15537,7 +15535,7 @@
         <v>45799</v>
       </c>
     </row>
-    <row r="541" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="541" spans="1:5">
       <c r="A541" t="s">
         <v>962</v>
       </c>
@@ -15548,20 +15546,20 @@
         <v>45799</v>
       </c>
     </row>
-    <row r="542" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="542" spans="1:5">
       <c r="A542" t="s">
         <v>962</v>
       </c>
       <c r="B542" t="s">
-        <v>1086</v>
+        <v>1089</v>
       </c>
       <c r="E542" s="12">
         <v>45799</v>
       </c>
     </row>
-    <row r="543" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="543" spans="1:5">
       <c r="A543" t="s">
-        <v>976</v>
+        <v>985</v>
       </c>
       <c r="B543" t="s">
         <v>320</v>
@@ -15570,9 +15568,9 @@
         <v>45799</v>
       </c>
     </row>
-    <row r="544" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="544" spans="1:5">
       <c r="A544" t="s">
-        <v>976</v>
+        <v>985</v>
       </c>
       <c r="B544" t="s">
         <v>204</v>
@@ -15581,9 +15579,9 @@
         <v>45800</v>
       </c>
     </row>
-    <row r="545" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="545" spans="1:5">
       <c r="A545" t="s">
-        <v>976</v>
+        <v>985</v>
       </c>
       <c r="B545" t="s">
         <v>820</v>
@@ -15592,9 +15590,9 @@
         <v>45804</v>
       </c>
     </row>
-    <row r="546" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="546" spans="1:5">
       <c r="A546" t="s">
-        <v>976</v>
+        <v>985</v>
       </c>
       <c r="B546" t="s">
         <v>390</v>
@@ -15604,9 +15602,9 @@
         <v>45807</v>
       </c>
     </row>
-    <row r="547" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="547" spans="1:5">
       <c r="A547" t="s">
-        <v>1076</v>
+        <v>1078</v>
       </c>
       <c r="B547" t="s">
         <v>390</v>
@@ -15616,9 +15614,9 @@
         <v>45807</v>
       </c>
     </row>
-    <row r="548" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="548" spans="1:5">
       <c r="A548" t="s">
-        <v>1076</v>
+        <v>1078</v>
       </c>
       <c r="B548" t="s">
         <v>163</v>
@@ -15627,7 +15625,7 @@
         <v>45808</v>
       </c>
     </row>
-    <row r="549" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="549" spans="1:5">
       <c r="A549" t="s">
         <v>967</v>
       </c>
@@ -15638,7 +15636,7 @@
         <v>45810</v>
       </c>
     </row>
-    <row r="550" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="550" spans="1:5">
       <c r="A550" t="s">
         <v>967</v>
       </c>
@@ -15649,7 +15647,7 @@
         <v>45810</v>
       </c>
     </row>
-    <row r="551" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="551" spans="1:5">
       <c r="A551" t="s">
         <v>967</v>
       </c>
@@ -15661,7 +15659,7 @@
         <v>45813</v>
       </c>
     </row>
-    <row r="552" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="552" spans="1:5">
       <c r="A552" t="s">
         <v>967</v>
       </c>
@@ -15673,7 +15671,7 @@
         <v>45813</v>
       </c>
     </row>
-    <row r="553" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="553" spans="1:5">
       <c r="A553" t="s">
         <v>967</v>
       </c>
@@ -15684,7 +15682,7 @@
         <v>45813</v>
       </c>
     </row>
-    <row r="554" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="554" spans="1:5">
       <c r="A554" t="s">
         <v>967</v>
       </c>
@@ -15695,9 +15693,9 @@
         <v>45813</v>
       </c>
     </row>
-    <row r="555" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="555" spans="1:5">
       <c r="A555" t="s">
-        <v>1084</v>
+        <v>1087</v>
       </c>
       <c r="B555" t="s">
         <v>163</v>
@@ -15706,7 +15704,7 @@
         <v>45813</v>
       </c>
     </row>
-    <row r="556" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="556" spans="1:5">
       <c r="A556" t="s">
         <v>962</v>
       </c>
@@ -15717,18 +15715,18 @@
         <v>45813</v>
       </c>
     </row>
-    <row r="557" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="557" spans="1:5">
       <c r="A557" t="s">
         <v>962</v>
       </c>
       <c r="B557" t="s">
-        <v>1086</v>
+        <v>1089</v>
       </c>
       <c r="E557" s="12">
         <v>45813</v>
       </c>
     </row>
-    <row r="558" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="558" spans="1:5">
       <c r="A558" t="s">
         <v>962</v>
       </c>
@@ -15739,7 +15737,7 @@
         <v>45813</v>
       </c>
     </row>
-    <row r="559" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="559" spans="1:5">
       <c r="A559" t="s">
         <v>962</v>
       </c>
@@ -15750,7 +15748,7 @@
         <v>45813</v>
       </c>
     </row>
-    <row r="560" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="560" spans="1:5">
       <c r="A560" t="s">
         <v>962</v>
       </c>
@@ -15761,7 +15759,7 @@
         <v>45813</v>
       </c>
     </row>
-    <row r="561" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="561" spans="1:5">
       <c r="A561" t="s">
         <v>962</v>
       </c>
@@ -15772,7 +15770,7 @@
         <v>45813</v>
       </c>
     </row>
-    <row r="562" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="562" spans="1:5">
       <c r="A562" t="s">
         <v>962</v>
       </c>
@@ -15783,7 +15781,7 @@
         <v>45813</v>
       </c>
     </row>
-    <row r="563" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="563" spans="1:5">
       <c r="A563" t="s">
         <v>962</v>
       </c>
@@ -15794,20 +15792,20 @@
         <v>45813</v>
       </c>
     </row>
-    <row r="564" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="564" spans="1:5">
       <c r="A564" t="s">
         <v>962</v>
       </c>
       <c r="B564" t="s">
-        <v>1045</v>
+        <v>1047</v>
       </c>
       <c r="E564" s="12">
         <v>45817</v>
       </c>
     </row>
-    <row r="565" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="565" spans="1:5">
       <c r="A565" t="s">
-        <v>976</v>
+        <v>985</v>
       </c>
       <c r="B565" t="s">
         <v>132</v>
@@ -15816,9 +15814,9 @@
         <v>45820</v>
       </c>
     </row>
-    <row r="566" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="566" spans="1:5">
       <c r="A566" t="s">
-        <v>976</v>
+        <v>985</v>
       </c>
       <c r="B566" t="s">
         <v>132</v>
@@ -15827,20 +15825,20 @@
         <v>45821</v>
       </c>
     </row>
-    <row r="567" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="567" spans="1:5">
       <c r="A567" t="s">
-        <v>976</v>
+        <v>985</v>
       </c>
       <c r="B567" t="s">
-        <v>1087</v>
+        <v>1090</v>
       </c>
       <c r="E567" s="12">
         <v>45824</v>
       </c>
     </row>
-    <row r="568" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="568" spans="1:5">
       <c r="A568" t="s">
-        <v>976</v>
+        <v>985</v>
       </c>
       <c r="B568" t="s">
         <v>505</v>
@@ -15849,9 +15847,9 @@
         <v>45824</v>
       </c>
     </row>
-    <row r="569" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="569" spans="1:5">
       <c r="A569" t="s">
-        <v>976</v>
+        <v>985</v>
       </c>
       <c r="B569" t="s">
         <v>814</v>
@@ -15860,9 +15858,9 @@
         <v>45824</v>
       </c>
     </row>
-    <row r="570" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="570" spans="1:5">
       <c r="A570" t="s">
-        <v>976</v>
+        <v>985</v>
       </c>
       <c r="B570" t="s">
         <v>274</v>
@@ -15871,29 +15869,29 @@
         <v>45824</v>
       </c>
     </row>
-    <row r="571" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="571" spans="1:5">
       <c r="A571" t="s">
-        <v>976</v>
+        <v>985</v>
       </c>
       <c r="B571" t="s">
-        <v>1086</v>
+        <v>1089</v>
       </c>
       <c r="E571" s="12">
         <v>45824</v>
       </c>
     </row>
-    <row r="572" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="572" spans="1:5">
       <c r="A572" t="s">
-        <v>976</v>
+        <v>985</v>
       </c>
       <c r="B572" t="s">
-        <v>1086</v>
+        <v>1089</v>
       </c>
       <c r="E572" s="12">
         <v>45824</v>
       </c>
     </row>
-    <row r="573" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="573" spans="1:5">
       <c r="A573" t="s">
         <v>962</v>
       </c>
@@ -15904,20 +15902,20 @@
         <v>45824</v>
       </c>
     </row>
-    <row r="574" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="574" spans="1:5">
       <c r="A574" t="s">
-        <v>976</v>
+        <v>985</v>
       </c>
       <c r="B574" t="s">
-        <v>1103</v>
+        <v>1091</v>
       </c>
       <c r="E574" s="12">
         <v>45825</v>
       </c>
     </row>
-    <row r="575" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="575" spans="1:5">
       <c r="A575" t="s">
-        <v>976</v>
+        <v>985</v>
       </c>
       <c r="B575" t="s">
         <v>117</v>
@@ -15926,9 +15924,9 @@
         <v>45826</v>
       </c>
     </row>
-    <row r="576" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="576" spans="1:5">
       <c r="A576" t="s">
-        <v>1076</v>
+        <v>1078</v>
       </c>
       <c r="B576" t="s">
         <v>87</v>
@@ -15937,9 +15935,9 @@
         <v>45827</v>
       </c>
     </row>
-    <row r="577" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="577" spans="1:5">
       <c r="A577" t="s">
-        <v>1076</v>
+        <v>1078</v>
       </c>
       <c r="B577" t="s">
         <v>96</v>
@@ -15948,9 +15946,9 @@
         <v>45827</v>
       </c>
     </row>
-    <row r="578" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="578" spans="1:5">
       <c r="A578" t="s">
-        <v>1076</v>
+        <v>1078</v>
       </c>
       <c r="B578" t="s">
         <v>46</v>
@@ -15960,9 +15958,9 @@
         <v>45828</v>
       </c>
     </row>
-    <row r="579" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="579" spans="1:5">
       <c r="A579" t="s">
-        <v>1076</v>
+        <v>1078</v>
       </c>
       <c r="B579" t="s">
         <v>61</v>
@@ -15971,29 +15969,29 @@
         <v>45828</v>
       </c>
     </row>
-    <row r="580" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="580" spans="1:5">
       <c r="A580" t="s">
-        <v>1076</v>
+        <v>1078</v>
       </c>
       <c r="B580" t="s">
-        <v>1085</v>
+        <v>1088</v>
       </c>
       <c r="E580" s="12">
         <v>45835</v>
       </c>
     </row>
-    <row r="581" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="581" spans="1:5">
       <c r="A581" t="s">
-        <v>1076</v>
+        <v>1078</v>
       </c>
       <c r="B581" t="s">
         <v>313</v>
       </c>
       <c r="E581" s="12" t="s">
-        <v>1088</v>
-      </c>
-    </row>
-    <row r="582" spans="1:5" x14ac:dyDescent="0.2">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="582" spans="1:5">
       <c r="A582" t="s">
         <v>967</v>
       </c>
@@ -16001,32 +15999,32 @@
         <v>61</v>
       </c>
       <c r="E582" s="12" t="s">
-        <v>1088</v>
-      </c>
-    </row>
-    <row r="583" spans="1:5" x14ac:dyDescent="0.2">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="583" spans="1:5">
       <c r="A583" t="s">
-        <v>1084</v>
+        <v>1087</v>
       </c>
       <c r="B583" t="s">
         <v>313</v>
       </c>
       <c r="E583" s="12" t="s">
-        <v>1089</v>
-      </c>
-    </row>
-    <row r="584" spans="1:5" x14ac:dyDescent="0.2">
+        <v>1093</v>
+      </c>
+    </row>
+    <row r="584" spans="1:5">
       <c r="A584" t="s">
         <v>967</v>
       </c>
       <c r="B584" t="s">
-        <v>1086</v>
+        <v>1089</v>
       </c>
       <c r="E584" s="12" t="s">
-        <v>1089</v>
-      </c>
-    </row>
-    <row r="585" spans="1:5" x14ac:dyDescent="0.2">
+        <v>1093</v>
+      </c>
+    </row>
+    <row r="585" spans="1:5">
       <c r="A585" t="s">
         <v>967</v>
       </c>
@@ -16034,10 +16032,10 @@
         <v>58</v>
       </c>
       <c r="E585" s="12" t="s">
-        <v>1090</v>
-      </c>
-    </row>
-    <row r="586" spans="1:5" x14ac:dyDescent="0.2">
+        <v>1094</v>
+      </c>
+    </row>
+    <row r="586" spans="1:5">
       <c r="A586" t="s">
         <v>967</v>
       </c>
@@ -16045,21 +16043,21 @@
         <v>144</v>
       </c>
       <c r="E586" s="12" t="s">
-        <v>1091</v>
-      </c>
-    </row>
-    <row r="587" spans="1:5" x14ac:dyDescent="0.2">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="587" spans="1:5">
       <c r="A587" t="s">
         <v>967</v>
       </c>
       <c r="B587" t="s">
-        <v>1092</v>
+        <v>1096</v>
       </c>
       <c r="E587" s="12" t="s">
-        <v>1091</v>
-      </c>
-    </row>
-    <row r="588" spans="1:5" x14ac:dyDescent="0.2">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="588" spans="1:5">
       <c r="A588" t="s">
         <v>967</v>
       </c>
@@ -16067,10 +16065,10 @@
         <v>412</v>
       </c>
       <c r="E588" s="12" t="s">
-        <v>1093</v>
-      </c>
-    </row>
-    <row r="589" spans="1:5" x14ac:dyDescent="0.2">
+        <v>1097</v>
+      </c>
+    </row>
+    <row r="589" spans="1:5">
       <c r="A589" t="s">
         <v>967</v>
       </c>
@@ -16078,21 +16076,21 @@
         <v>52</v>
       </c>
       <c r="E589" s="12" t="s">
-        <v>1094</v>
-      </c>
-    </row>
-    <row r="590" spans="1:5" x14ac:dyDescent="0.2">
+        <v>1098</v>
+      </c>
+    </row>
+    <row r="590" spans="1:5">
       <c r="A590" t="s">
-        <v>976</v>
+        <v>985</v>
       </c>
       <c r="B590" t="s">
-        <v>1095</v>
+        <v>1099</v>
       </c>
       <c r="E590" s="12" t="s">
-        <v>1096</v>
-      </c>
-    </row>
-    <row r="591" spans="1:5" x14ac:dyDescent="0.2">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="591" spans="1:5">
       <c r="A591" t="s">
         <v>962</v>
       </c>
@@ -16103,20 +16101,20 @@
         <v>45843</v>
       </c>
     </row>
-    <row r="592" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="592" spans="1:5">
       <c r="A592" t="s">
         <v>962</v>
       </c>
       <c r="B592" t="s">
-        <v>1103</v>
+        <v>1091</v>
       </c>
       <c r="E592" s="12">
         <v>45861</v>
       </c>
     </row>
-    <row r="593" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="593" spans="1:5">
       <c r="A593" t="s">
-        <v>976</v>
+        <v>985</v>
       </c>
       <c r="B593" t="s">
         <v>176</v>
@@ -16125,9 +16123,9 @@
         <v>45861</v>
       </c>
     </row>
-    <row r="594" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="594" spans="1:5">
       <c r="A594" t="s">
-        <v>1076</v>
+        <v>1078</v>
       </c>
       <c r="B594" s="20" t="s">
         <v>166</v>
@@ -16136,9 +16134,9 @@
         <v>45843</v>
       </c>
     </row>
-    <row r="595" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="595" spans="1:5">
       <c r="A595" t="s">
-        <v>1076</v>
+        <v>1078</v>
       </c>
       <c r="B595" s="20" t="s">
         <v>38</v>
@@ -16147,34 +16145,34 @@
         <v>45843</v>
       </c>
     </row>
-    <row r="596" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="596" spans="1:5">
       <c r="A596" t="s">
-        <v>1076</v>
+        <v>1078</v>
       </c>
       <c r="B596" t="s">
-        <v>1085</v>
+        <v>1088</v>
       </c>
       <c r="E596" s="12">
         <v>45861</v>
       </c>
     </row>
-    <row r="597" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="597" spans="1:5">
       <c r="A597" t="s">
         <v>967</v>
       </c>
       <c r="B597" t="s">
-        <v>1097</v>
+        <v>1101</v>
       </c>
       <c r="E597" s="12" t="s">
-        <v>1098</v>
-      </c>
-    </row>
-    <row r="598" spans="1:5" x14ac:dyDescent="0.2">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="598" spans="1:5">
       <c r="A598" t="s">
-        <v>1076</v>
+        <v>1078</v>
       </c>
       <c r="B598" t="s">
-        <v>1099</v>
+        <v>1103</v>
       </c>
       <c r="E598" s="12">
         <v>45895</v>
@@ -16196,6 +16194,28 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <ProjectRole xmlns="b238fc39-fcbb-4f8c-bfd3-e3a789f7784e" xsi:nil="true"/>
+    <Notes xmlns="b238fc39-fcbb-4f8c-bfd3-e3a789f7784e" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b238fc39-fcbb-4f8c-bfd3-e3a789f7784e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="ccd2e96c-ba06-41a4-9d14-ee5d4767a409" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101002B87155CDAEBE54E8A991CDFF09FE870" ma:contentTypeVersion="21" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="07d22f826efb92a1b7f7a52cdc9ab0c0">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="ccd2e96c-ba06-41a4-9d14-ee5d4767a409" xmlns:ns3="b238fc39-fcbb-4f8c-bfd3-e3a789f7784e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="8f50f4dd1661db9c8120150ec829b0b2" ns2:_="" ns3:_="">
     <xsd:import namespace="ccd2e96c-ba06-41a4-9d14-ee5d4767a409"/>
@@ -16469,68 +16489,14 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <ProjectRole xmlns="b238fc39-fcbb-4f8c-bfd3-e3a789f7784e" xsi:nil="true"/>
-    <Notes xmlns="b238fc39-fcbb-4f8c-bfd3-e3a789f7784e" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b238fc39-fcbb-4f8c-bfd3-e3a789f7784e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="ccd2e96c-ba06-41a4-9d14-ee5d4767a409" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{25367526-E489-4070-A4F8-E19860E9B429}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="ccd2e96c-ba06-41a4-9d14-ee5d4767a409"/>
-    <ds:schemaRef ds:uri="b238fc39-fcbb-4f8c-bfd3-e3a789f7784e"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{402EE481-94FD-4951-81DD-5A65E38D7030}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B14276B6-F2F9-47B2-B61C-C247CB20D655}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="b238fc39-fcbb-4f8c-bfd3-e3a789f7784e"/>
-    <ds:schemaRef ds:uri="ccd2e96c-ba06-41a4-9d14-ee5d4767a409"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B14276B6-F2F9-47B2-B61C-C247CB20D655}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{402EE481-94FD-4951-81DD-5A65E38D7030}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{25367526-E489-4070-A4F8-E19860E9B429}"/>
 </file>